--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -112,8 +118,13 @@
         <fgColor rgb="008B1E22"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,11 +190,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -351,6 +376,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,11 +624,18 @@
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
+        <t>▣ 외주
+입고일
+(직접 입력)</t>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
         <t>▣ 상태
 (직접 입력)</t>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모
 (직접 입력)</t>
@@ -885,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q140"/>
+  <dimension ref="A1:R140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -903,12 +953,13 @@
     <col width="10" customWidth="1" style="43" min="13" max="13"/>
     <col width="6" customWidth="1" style="43" min="14" max="14"/>
     <col width="6" customWidth="1" style="43" min="15" max="15"/>
-    <col width="10" customWidth="1" style="43" min="16" max="16"/>
-    <col width="28" customWidth="1" style="43" min="17" max="17"/>
+    <col width="12" customWidth="1" style="43" min="16" max="16"/>
+    <col width="10" customWidth="1" style="43" min="17" max="17"/>
+    <col width="28" customWidth="1" style="43" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -928,10 +979,11 @@
       <c r="N1" s="16" t="n"/>
       <c r="O1" s="16" t="n"/>
       <c r="P1" s="16" t="n"/>
-      <c r="Q1" s="17" t="n"/>
+      <c r="Q1" s="16" t="n"/>
+      <c r="R1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -950,10 +1002,11 @@
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="16" t="n"/>
       <c r="O2" s="16" t="n"/>
-      <c r="P2" s="17" t="n"/>
-      <c r="Q2" s="55" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:44</t>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="17" t="n"/>
+      <c r="R2" s="60" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1086,17 @@
           <t>✏입력</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1120,12 +1178,18 @@
           <t>입고</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="P4" s="61" t="inlineStr">
+        <is>
+          <t>외주
+입고일</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1182,7 +1246,8 @@
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="22" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1235,7 +1300,8 @@
       <c r="N6" s="15" t="n"/>
       <c r="O6" s="15" t="n"/>
       <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="24" t="n"/>
+      <c r="Q6" s="13" t="n"/>
+      <c r="R6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1288,7 +1354,8 @@
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="22" t="n"/>
+      <c r="Q7" s="9" t="n"/>
+      <c r="R7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1341,7 +1408,8 @@
       <c r="N8" s="15" t="n"/>
       <c r="O8" s="15" t="n"/>
       <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="24" t="n"/>
+      <c r="Q8" s="13" t="n"/>
+      <c r="R8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1394,7 +1462,8 @@
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
       <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="22" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1447,7 +1516,8 @@
       <c r="N10" s="15" t="n"/>
       <c r="O10" s="15" t="n"/>
       <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="24" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1500,7 +1570,8 @@
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="22" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1553,7 +1624,8 @@
       <c r="N12" s="15" t="n"/>
       <c r="O12" s="15" t="n"/>
       <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="24" t="n"/>
+      <c r="Q12" s="13" t="n"/>
+      <c r="R12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1606,7 +1678,8 @@
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="22" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1659,7 +1732,8 @@
       <c r="N14" s="15" t="n"/>
       <c r="O14" s="15" t="n"/>
       <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="24" t="n"/>
+      <c r="Q14" s="13" t="n"/>
+      <c r="R14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1712,7 +1786,8 @@
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="11" t="n"/>
       <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="22" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1765,7 +1840,8 @@
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
       <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="24" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -1818,7 +1894,8 @@
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="11" t="n"/>
       <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="22" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -1871,7 +1948,8 @@
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
       <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="24" t="n"/>
+      <c r="Q18" s="13" t="n"/>
+      <c r="R18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -1924,7 +2002,8 @@
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="11" t="n"/>
       <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="22" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -1977,7 +2056,8 @@
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
       <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="24" t="n"/>
+      <c r="Q20" s="13" t="n"/>
+      <c r="R20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2030,7 +2110,8 @@
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="11" t="n"/>
       <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="22" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2083,7 +2164,8 @@
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
       <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="24" t="n"/>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2136,7 +2218,8 @@
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="11" t="n"/>
       <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="22" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2189,7 +2272,8 @@
       <c r="N24" s="15" t="n"/>
       <c r="O24" s="15" t="n"/>
       <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="24" t="n"/>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2242,7 +2326,8 @@
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="11" t="n"/>
       <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="22" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2295,7 +2380,8 @@
       <c r="N26" s="15" t="n"/>
       <c r="O26" s="15" t="n"/>
       <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="24" t="n"/>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2348,7 +2434,8 @@
       <c r="N27" s="11" t="n"/>
       <c r="O27" s="11" t="n"/>
       <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="22" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n">
@@ -2401,7 +2488,8 @@
       <c r="N28" s="15" t="n"/>
       <c r="O28" s="15" t="n"/>
       <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="24" t="n"/>
+      <c r="Q28" s="13" t="n"/>
+      <c r="R28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -2454,7 +2542,8 @@
       <c r="N29" s="11" t="n"/>
       <c r="O29" s="11" t="n"/>
       <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="22" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n">
@@ -2507,7 +2596,8 @@
       <c r="N30" s="15" t="n"/>
       <c r="O30" s="15" t="n"/>
       <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="24" t="n"/>
+      <c r="Q30" s="13" t="n"/>
+      <c r="R30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -2560,7 +2650,8 @@
       <c r="N31" s="11" t="n"/>
       <c r="O31" s="11" t="n"/>
       <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="22" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n">
@@ -2613,7 +2704,8 @@
       <c r="N32" s="15" t="n"/>
       <c r="O32" s="15" t="n"/>
       <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="24" t="n"/>
+      <c r="Q32" s="13" t="n"/>
+      <c r="R32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -2666,7 +2758,8 @@
       <c r="N33" s="11" t="n"/>
       <c r="O33" s="11" t="n"/>
       <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="22" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n">
@@ -2719,7 +2812,8 @@
       <c r="N34" s="15" t="n"/>
       <c r="O34" s="15" t="n"/>
       <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="24" t="n"/>
+      <c r="Q34" s="13" t="n"/>
+      <c r="R34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -2772,7 +2866,8 @@
       <c r="N35" s="11" t="n"/>
       <c r="O35" s="11" t="n"/>
       <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="22" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n">
@@ -2825,7 +2920,8 @@
       <c r="N36" s="15" t="n"/>
       <c r="O36" s="15" t="n"/>
       <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="24" t="n"/>
+      <c r="Q36" s="13" t="n"/>
+      <c r="R36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -2878,7 +2974,8 @@
       <c r="N37" s="11" t="n"/>
       <c r="O37" s="11" t="n"/>
       <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="22" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n">
@@ -2931,7 +3028,8 @@
       <c r="N38" s="15" t="n"/>
       <c r="O38" s="15" t="n"/>
       <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="24" t="n"/>
+      <c r="Q38" s="13" t="n"/>
+      <c r="R38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -2984,7 +3082,8 @@
       <c r="N39" s="11" t="n"/>
       <c r="O39" s="11" t="n"/>
       <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="22" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n">
@@ -3037,7 +3136,8 @@
       <c r="N40" s="15" t="n"/>
       <c r="O40" s="15" t="n"/>
       <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="24" t="n"/>
+      <c r="Q40" s="13" t="n"/>
+      <c r="R40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -3090,7 +3190,8 @@
       <c r="N41" s="11" t="n"/>
       <c r="O41" s="11" t="n"/>
       <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="22" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n">
@@ -3143,7 +3244,8 @@
       <c r="N42" s="15" t="n"/>
       <c r="O42" s="15" t="n"/>
       <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="24" t="n"/>
+      <c r="Q42" s="13" t="n"/>
+      <c r="R42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -3196,7 +3298,8 @@
       <c r="N43" s="11" t="n"/>
       <c r="O43" s="11" t="n"/>
       <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="22" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n">
@@ -3249,7 +3352,8 @@
       <c r="N44" s="15" t="n"/>
       <c r="O44" s="15" t="n"/>
       <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="24" t="n"/>
+      <c r="Q44" s="13" t="n"/>
+      <c r="R44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -3302,7 +3406,8 @@
       <c r="N45" s="11" t="n"/>
       <c r="O45" s="11" t="n"/>
       <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="22" t="n"/>
+      <c r="Q45" s="9" t="n"/>
+      <c r="R45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n">
@@ -3355,7 +3460,8 @@
       <c r="N46" s="15" t="n"/>
       <c r="O46" s="15" t="n"/>
       <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="24" t="n"/>
+      <c r="Q46" s="13" t="n"/>
+      <c r="R46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -3408,7 +3514,8 @@
       <c r="N47" s="11" t="n"/>
       <c r="O47" s="11" t="n"/>
       <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="22" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n">
@@ -3461,7 +3568,8 @@
       <c r="N48" s="15" t="n"/>
       <c r="O48" s="15" t="n"/>
       <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="24" t="n"/>
+      <c r="Q48" s="13" t="n"/>
+      <c r="R48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -3514,7 +3622,8 @@
       <c r="N49" s="11" t="n"/>
       <c r="O49" s="11" t="n"/>
       <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="22" t="n"/>
+      <c r="Q49" s="9" t="n"/>
+      <c r="R49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n">
@@ -3567,7 +3676,8 @@
       <c r="N50" s="15" t="n"/>
       <c r="O50" s="15" t="n"/>
       <c r="P50" s="13" t="n"/>
-      <c r="Q50" s="24" t="n"/>
+      <c r="Q50" s="13" t="n"/>
+      <c r="R50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -3620,7 +3730,8 @@
       <c r="N51" s="11" t="n"/>
       <c r="O51" s="11" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="22" t="n"/>
+      <c r="Q51" s="9" t="n"/>
+      <c r="R51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -3673,7 +3784,8 @@
       <c r="N52" s="15" t="n"/>
       <c r="O52" s="15" t="n"/>
       <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="24" t="n"/>
+      <c r="Q52" s="13" t="n"/>
+      <c r="R52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -3726,7 +3838,8 @@
       <c r="N53" s="11" t="n"/>
       <c r="O53" s="11" t="n"/>
       <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="22" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+      <c r="R53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n">
@@ -3779,7 +3892,8 @@
       <c r="N54" s="15" t="n"/>
       <c r="O54" s="15" t="n"/>
       <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="24" t="n"/>
+      <c r="Q54" s="13" t="n"/>
+      <c r="R54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -3832,7 +3946,8 @@
       <c r="N55" s="11" t="n"/>
       <c r="O55" s="11" t="n"/>
       <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="22" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n">
@@ -3885,7 +4000,8 @@
       <c r="N56" s="15" t="n"/>
       <c r="O56" s="15" t="n"/>
       <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="24" t="n"/>
+      <c r="Q56" s="13" t="n"/>
+      <c r="R56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -3938,7 +4054,8 @@
       <c r="N57" s="11" t="n"/>
       <c r="O57" s="11" t="n"/>
       <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="22" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+      <c r="R57" s="22" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -3991,7 +4108,8 @@
       <c r="N58" s="15" t="n"/>
       <c r="O58" s="15" t="n"/>
       <c r="P58" s="13" t="n"/>
-      <c r="Q58" s="24" t="n"/>
+      <c r="Q58" s="13" t="n"/>
+      <c r="R58" s="24" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -4044,7 +4162,8 @@
       <c r="N59" s="11" t="n"/>
       <c r="O59" s="11" t="n"/>
       <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="22" t="n"/>
+      <c r="Q59" s="9" t="n"/>
+      <c r="R59" s="22" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="12" t="n">
@@ -4097,7 +4216,8 @@
       <c r="N60" s="15" t="n"/>
       <c r="O60" s="15" t="n"/>
       <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="24" t="n"/>
+      <c r="Q60" s="13" t="n"/>
+      <c r="R60" s="24" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -4150,7 +4270,8 @@
       <c r="N61" s="11" t="n"/>
       <c r="O61" s="11" t="n"/>
       <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="22" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="22" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="12" t="n">
@@ -4203,7 +4324,8 @@
       <c r="N62" s="15" t="n"/>
       <c r="O62" s="15" t="n"/>
       <c r="P62" s="13" t="n"/>
-      <c r="Q62" s="24" t="n"/>
+      <c r="Q62" s="13" t="n"/>
+      <c r="R62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -4256,7 +4378,8 @@
       <c r="N63" s="11" t="n"/>
       <c r="O63" s="11" t="n"/>
       <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="22" t="n"/>
+      <c r="Q63" s="9" t="n"/>
+      <c r="R63" s="22" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="12" t="n">
@@ -4309,7 +4432,8 @@
       <c r="N64" s="15" t="n"/>
       <c r="O64" s="15" t="n"/>
       <c r="P64" s="13" t="n"/>
-      <c r="Q64" s="24" t="n"/>
+      <c r="Q64" s="13" t="n"/>
+      <c r="R64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="8" t="n">
@@ -4362,7 +4486,8 @@
       <c r="N65" s="11" t="n"/>
       <c r="O65" s="11" t="n"/>
       <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="22" t="n"/>
+      <c r="Q65" s="9" t="n"/>
+      <c r="R65" s="22" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="12" t="n">
@@ -4415,7 +4540,8 @@
       <c r="N66" s="15" t="n"/>
       <c r="O66" s="15" t="n"/>
       <c r="P66" s="13" t="n"/>
-      <c r="Q66" s="24" t="n"/>
+      <c r="Q66" s="13" t="n"/>
+      <c r="R66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="8" t="n">
@@ -4468,7 +4594,8 @@
       <c r="N67" s="11" t="n"/>
       <c r="O67" s="11" t="n"/>
       <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="22" t="n"/>
+      <c r="Q67" s="9" t="n"/>
+      <c r="R67" s="22" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="12" t="n">
@@ -4521,7 +4648,8 @@
       <c r="N68" s="15" t="n"/>
       <c r="O68" s="15" t="n"/>
       <c r="P68" s="13" t="n"/>
-      <c r="Q68" s="24" t="n"/>
+      <c r="Q68" s="13" t="n"/>
+      <c r="R68" s="24" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="8" t="n">
@@ -4574,7 +4702,8 @@
       <c r="N69" s="11" t="n"/>
       <c r="O69" s="11" t="n"/>
       <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="22" t="n"/>
+      <c r="Q69" s="9" t="n"/>
+      <c r="R69" s="22" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="12" t="n">
@@ -4627,7 +4756,8 @@
       <c r="N70" s="15" t="n"/>
       <c r="O70" s="15" t="n"/>
       <c r="P70" s="13" t="n"/>
-      <c r="Q70" s="24" t="n"/>
+      <c r="Q70" s="13" t="n"/>
+      <c r="R70" s="24" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="8" t="n">
@@ -4680,7 +4810,8 @@
       <c r="N71" s="11" t="n"/>
       <c r="O71" s="11" t="n"/>
       <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="22" t="n"/>
+      <c r="Q71" s="9" t="n"/>
+      <c r="R71" s="22" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="12" t="n">
@@ -4733,7 +4864,8 @@
       <c r="N72" s="15" t="n"/>
       <c r="O72" s="15" t="n"/>
       <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="24" t="n"/>
+      <c r="Q72" s="13" t="n"/>
+      <c r="R72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="8" t="n">
@@ -4786,7 +4918,8 @@
       <c r="N73" s="11" t="n"/>
       <c r="O73" s="11" t="n"/>
       <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="22" t="n"/>
+      <c r="Q73" s="9" t="n"/>
+      <c r="R73" s="22" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="12" t="n">
@@ -4839,7 +4972,8 @@
       <c r="N74" s="15" t="n"/>
       <c r="O74" s="15" t="n"/>
       <c r="P74" s="13" t="n"/>
-      <c r="Q74" s="24" t="n"/>
+      <c r="Q74" s="13" t="n"/>
+      <c r="R74" s="24" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="n">
@@ -4892,7 +5026,8 @@
       <c r="N75" s="11" t="n"/>
       <c r="O75" s="11" t="n"/>
       <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="22" t="n"/>
+      <c r="Q75" s="9" t="n"/>
+      <c r="R75" s="22" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="12" t="n">
@@ -4945,7 +5080,8 @@
       <c r="N76" s="15" t="n"/>
       <c r="O76" s="15" t="n"/>
       <c r="P76" s="13" t="n"/>
-      <c r="Q76" s="24" t="n"/>
+      <c r="Q76" s="13" t="n"/>
+      <c r="R76" s="24" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="8" t="n">
@@ -4998,7 +5134,8 @@
       <c r="N77" s="11" t="n"/>
       <c r="O77" s="11" t="n"/>
       <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="22" t="n"/>
+      <c r="Q77" s="9" t="n"/>
+      <c r="R77" s="22" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="12" t="n">
@@ -5051,7 +5188,8 @@
       <c r="N78" s="15" t="n"/>
       <c r="O78" s="15" t="n"/>
       <c r="P78" s="13" t="n"/>
-      <c r="Q78" s="24" t="n"/>
+      <c r="Q78" s="13" t="n"/>
+      <c r="R78" s="24" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="8" t="n">
@@ -5104,7 +5242,8 @@
       <c r="N79" s="11" t="n"/>
       <c r="O79" s="11" t="n"/>
       <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="22" t="n"/>
+      <c r="Q79" s="9" t="n"/>
+      <c r="R79" s="22" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="12" t="n">
@@ -5157,7 +5296,8 @@
       <c r="N80" s="15" t="n"/>
       <c r="O80" s="15" t="n"/>
       <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="24" t="n"/>
+      <c r="Q80" s="13" t="n"/>
+      <c r="R80" s="24" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="8" t="n">
@@ -5210,7 +5350,8 @@
       <c r="N81" s="11" t="n"/>
       <c r="O81" s="11" t="n"/>
       <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="22" t="n"/>
+      <c r="Q81" s="9" t="n"/>
+      <c r="R81" s="22" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="12" t="n">
@@ -5263,7 +5404,8 @@
       <c r="N82" s="15" t="n"/>
       <c r="O82" s="15" t="n"/>
       <c r="P82" s="13" t="n"/>
-      <c r="Q82" s="24" t="n"/>
+      <c r="Q82" s="13" t="n"/>
+      <c r="R82" s="24" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="8" t="n">
@@ -5316,7 +5458,8 @@
       <c r="N83" s="11" t="n"/>
       <c r="O83" s="11" t="n"/>
       <c r="P83" s="9" t="n"/>
-      <c r="Q83" s="22" t="n"/>
+      <c r="Q83" s="9" t="n"/>
+      <c r="R83" s="22" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -5369,7 +5512,8 @@
       <c r="N84" s="15" t="n"/>
       <c r="O84" s="15" t="n"/>
       <c r="P84" s="13" t="n"/>
-      <c r="Q84" s="24" t="n"/>
+      <c r="Q84" s="13" t="n"/>
+      <c r="R84" s="24" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="8" t="n">
@@ -5422,7 +5566,8 @@
       <c r="N85" s="11" t="n"/>
       <c r="O85" s="11" t="n"/>
       <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="22" t="n"/>
+      <c r="Q85" s="9" t="n"/>
+      <c r="R85" s="22" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="12" t="n">
@@ -5475,7 +5620,8 @@
       <c r="N86" s="15" t="n"/>
       <c r="O86" s="15" t="n"/>
       <c r="P86" s="13" t="n"/>
-      <c r="Q86" s="24" t="n"/>
+      <c r="Q86" s="13" t="n"/>
+      <c r="R86" s="24" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -5528,7 +5674,8 @@
       <c r="N87" s="11" t="n"/>
       <c r="O87" s="11" t="n"/>
       <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="22" t="n"/>
+      <c r="Q87" s="9" t="n"/>
+      <c r="R87" s="22" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="12" t="n">
@@ -5581,7 +5728,8 @@
       <c r="N88" s="15" t="n"/>
       <c r="O88" s="15" t="n"/>
       <c r="P88" s="13" t="n"/>
-      <c r="Q88" s="24" t="n"/>
+      <c r="Q88" s="13" t="n"/>
+      <c r="R88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="8" t="n">
@@ -5634,7 +5782,8 @@
       <c r="N89" s="11" t="n"/>
       <c r="O89" s="11" t="n"/>
       <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="22" t="n"/>
+      <c r="Q89" s="9" t="n"/>
+      <c r="R89" s="22" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="12" t="n">
@@ -5687,7 +5836,8 @@
       <c r="N90" s="15" t="n"/>
       <c r="O90" s="15" t="n"/>
       <c r="P90" s="13" t="n"/>
-      <c r="Q90" s="24" t="n"/>
+      <c r="Q90" s="13" t="n"/>
+      <c r="R90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="8" t="n">
@@ -5740,7 +5890,8 @@
       <c r="N91" s="11" t="n"/>
       <c r="O91" s="11" t="n"/>
       <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="22" t="n"/>
+      <c r="Q91" s="9" t="n"/>
+      <c r="R91" s="22" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="12" t="n">
@@ -5793,7 +5944,8 @@
       <c r="N92" s="15" t="n"/>
       <c r="O92" s="15" t="n"/>
       <c r="P92" s="13" t="n"/>
-      <c r="Q92" s="24" t="n"/>
+      <c r="Q92" s="13" t="n"/>
+      <c r="R92" s="24" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="8" t="n">
@@ -5846,7 +5998,8 @@
       <c r="N93" s="11" t="n"/>
       <c r="O93" s="11" t="n"/>
       <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="22" t="n"/>
+      <c r="Q93" s="9" t="n"/>
+      <c r="R93" s="22" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="12" t="n">
@@ -5899,7 +6052,8 @@
       <c r="N94" s="15" t="n"/>
       <c r="O94" s="15" t="n"/>
       <c r="P94" s="13" t="n"/>
-      <c r="Q94" s="24" t="n"/>
+      <c r="Q94" s="13" t="n"/>
+      <c r="R94" s="24" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="8" t="n">
@@ -5952,7 +6106,8 @@
       <c r="N95" s="11" t="n"/>
       <c r="O95" s="11" t="n"/>
       <c r="P95" s="9" t="n"/>
-      <c r="Q95" s="22" t="n"/>
+      <c r="Q95" s="9" t="n"/>
+      <c r="R95" s="22" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="n">
@@ -6005,7 +6160,8 @@
       <c r="N96" s="15" t="n"/>
       <c r="O96" s="15" t="n"/>
       <c r="P96" s="13" t="n"/>
-      <c r="Q96" s="24" t="n"/>
+      <c r="Q96" s="13" t="n"/>
+      <c r="R96" s="24" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="8" t="n">
@@ -6058,7 +6214,8 @@
       <c r="N97" s="11" t="n"/>
       <c r="O97" s="11" t="n"/>
       <c r="P97" s="9" t="n"/>
-      <c r="Q97" s="22" t="n"/>
+      <c r="Q97" s="9" t="n"/>
+      <c r="R97" s="22" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="n">
@@ -6111,7 +6268,8 @@
       <c r="N98" s="15" t="n"/>
       <c r="O98" s="15" t="n"/>
       <c r="P98" s="13" t="n"/>
-      <c r="Q98" s="24" t="n"/>
+      <c r="Q98" s="13" t="n"/>
+      <c r="R98" s="24" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -6164,7 +6322,8 @@
       <c r="N99" s="11" t="n"/>
       <c r="O99" s="11" t="n"/>
       <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="22" t="n"/>
+      <c r="Q99" s="9" t="n"/>
+      <c r="R99" s="22" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="n">
@@ -6217,7 +6376,8 @@
       <c r="N100" s="15" t="n"/>
       <c r="O100" s="15" t="n"/>
       <c r="P100" s="13" t="n"/>
-      <c r="Q100" s="24" t="n"/>
+      <c r="Q100" s="13" t="n"/>
+      <c r="R100" s="24" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="8" t="n">
@@ -6270,7 +6430,8 @@
       <c r="N101" s="11" t="n"/>
       <c r="O101" s="11" t="n"/>
       <c r="P101" s="9" t="n"/>
-      <c r="Q101" s="22" t="n"/>
+      <c r="Q101" s="9" t="n"/>
+      <c r="R101" s="22" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="n">
@@ -6323,7 +6484,8 @@
       <c r="N102" s="15" t="n"/>
       <c r="O102" s="15" t="n"/>
       <c r="P102" s="13" t="n"/>
-      <c r="Q102" s="24" t="n"/>
+      <c r="Q102" s="13" t="n"/>
+      <c r="R102" s="24" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="8" t="n">
@@ -6376,7 +6538,8 @@
       <c r="N103" s="11" t="n"/>
       <c r="O103" s="11" t="n"/>
       <c r="P103" s="9" t="n"/>
-      <c r="Q103" s="22" t="n"/>
+      <c r="Q103" s="9" t="n"/>
+      <c r="R103" s="22" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="n">
@@ -6429,7 +6592,8 @@
       <c r="N104" s="15" t="n"/>
       <c r="O104" s="15" t="n"/>
       <c r="P104" s="13" t="n"/>
-      <c r="Q104" s="24" t="n"/>
+      <c r="Q104" s="13" t="n"/>
+      <c r="R104" s="24" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="8" t="n">
@@ -6482,7 +6646,8 @@
       <c r="N105" s="11" t="n"/>
       <c r="O105" s="11" t="n"/>
       <c r="P105" s="9" t="n"/>
-      <c r="Q105" s="22" t="n"/>
+      <c r="Q105" s="9" t="n"/>
+      <c r="R105" s="22" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="n">
@@ -6535,7 +6700,8 @@
       <c r="N106" s="15" t="n"/>
       <c r="O106" s="15" t="n"/>
       <c r="P106" s="13" t="n"/>
-      <c r="Q106" s="24" t="n"/>
+      <c r="Q106" s="13" t="n"/>
+      <c r="R106" s="24" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -6588,7 +6754,8 @@
       <c r="N107" s="11" t="n"/>
       <c r="O107" s="11" t="n"/>
       <c r="P107" s="9" t="n"/>
-      <c r="Q107" s="22" t="n"/>
+      <c r="Q107" s="9" t="n"/>
+      <c r="R107" s="22" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -6641,7 +6808,8 @@
       <c r="N108" s="15" t="n"/>
       <c r="O108" s="15" t="n"/>
       <c r="P108" s="13" t="n"/>
-      <c r="Q108" s="24" t="n"/>
+      <c r="Q108" s="13" t="n"/>
+      <c r="R108" s="24" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="8" t="n">
@@ -6690,7 +6858,8 @@
       <c r="N109" s="9" t="n"/>
       <c r="O109" s="9" t="n"/>
       <c r="P109" s="9" t="n"/>
-      <c r="Q109" s="22" t="n"/>
+      <c r="Q109" s="9" t="n"/>
+      <c r="R109" s="22" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="n">
@@ -6731,7 +6900,8 @@
       <c r="N110" s="13" t="n"/>
       <c r="O110" s="13" t="n"/>
       <c r="P110" s="13" t="n"/>
-      <c r="Q110" s="24" t="n"/>
+      <c r="Q110" s="13" t="n"/>
+      <c r="R110" s="24" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="8" t="n"/>
@@ -6750,7 +6920,8 @@
       <c r="N111" s="9" t="n"/>
       <c r="O111" s="9" t="n"/>
       <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="22" t="n"/>
+      <c r="Q111" s="9" t="n"/>
+      <c r="R111" s="22" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="n"/>
@@ -6769,7 +6940,8 @@
       <c r="N112" s="13" t="n"/>
       <c r="O112" s="13" t="n"/>
       <c r="P112" s="13" t="n"/>
-      <c r="Q112" s="24" t="n"/>
+      <c r="Q112" s="13" t="n"/>
+      <c r="R112" s="24" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="8" t="n"/>
@@ -6788,7 +6960,8 @@
       <c r="N113" s="9" t="n"/>
       <c r="O113" s="9" t="n"/>
       <c r="P113" s="9" t="n"/>
-      <c r="Q113" s="22" t="n"/>
+      <c r="Q113" s="9" t="n"/>
+      <c r="R113" s="22" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="n"/>
@@ -6807,7 +6980,8 @@
       <c r="N114" s="13" t="n"/>
       <c r="O114" s="13" t="n"/>
       <c r="P114" s="13" t="n"/>
-      <c r="Q114" s="24" t="n"/>
+      <c r="Q114" s="13" t="n"/>
+      <c r="R114" s="24" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="8" t="n"/>
@@ -6826,7 +7000,8 @@
       <c r="N115" s="9" t="n"/>
       <c r="O115" s="9" t="n"/>
       <c r="P115" s="9" t="n"/>
-      <c r="Q115" s="22" t="n"/>
+      <c r="Q115" s="9" t="n"/>
+      <c r="R115" s="22" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="n"/>
@@ -6845,7 +7020,8 @@
       <c r="N116" s="13" t="n"/>
       <c r="O116" s="13" t="n"/>
       <c r="P116" s="13" t="n"/>
-      <c r="Q116" s="24" t="n"/>
+      <c r="Q116" s="13" t="n"/>
+      <c r="R116" s="24" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="8" t="n"/>
@@ -6864,7 +7040,8 @@
       <c r="N117" s="9" t="n"/>
       <c r="O117" s="9" t="n"/>
       <c r="P117" s="9" t="n"/>
-      <c r="Q117" s="22" t="n"/>
+      <c r="Q117" s="9" t="n"/>
+      <c r="R117" s="22" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="12" t="n"/>
@@ -6883,7 +7060,8 @@
       <c r="N118" s="13" t="n"/>
       <c r="O118" s="13" t="n"/>
       <c r="P118" s="13" t="n"/>
-      <c r="Q118" s="24" t="n"/>
+      <c r="Q118" s="13" t="n"/>
+      <c r="R118" s="24" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="8" t="n"/>
@@ -6902,7 +7080,8 @@
       <c r="N119" s="9" t="n"/>
       <c r="O119" s="9" t="n"/>
       <c r="P119" s="9" t="n"/>
-      <c r="Q119" s="22" t="n"/>
+      <c r="Q119" s="9" t="n"/>
+      <c r="R119" s="22" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="n"/>
@@ -6921,7 +7100,8 @@
       <c r="N120" s="13" t="n"/>
       <c r="O120" s="13" t="n"/>
       <c r="P120" s="13" t="n"/>
-      <c r="Q120" s="24" t="n"/>
+      <c r="Q120" s="13" t="n"/>
+      <c r="R120" s="24" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="8" t="n"/>
@@ -6940,7 +7120,8 @@
       <c r="N121" s="9" t="n"/>
       <c r="O121" s="9" t="n"/>
       <c r="P121" s="9" t="n"/>
-      <c r="Q121" s="22" t="n"/>
+      <c r="Q121" s="9" t="n"/>
+      <c r="R121" s="22" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="n"/>
@@ -6959,7 +7140,8 @@
       <c r="N122" s="13" t="n"/>
       <c r="O122" s="13" t="n"/>
       <c r="P122" s="13" t="n"/>
-      <c r="Q122" s="24" t="n"/>
+      <c r="Q122" s="13" t="n"/>
+      <c r="R122" s="24" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="8" t="n"/>
@@ -6978,7 +7160,8 @@
       <c r="N123" s="9" t="n"/>
       <c r="O123" s="9" t="n"/>
       <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="22" t="n"/>
+      <c r="Q123" s="9" t="n"/>
+      <c r="R123" s="22" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="n"/>
@@ -6997,7 +7180,8 @@
       <c r="N124" s="13" t="n"/>
       <c r="O124" s="13" t="n"/>
       <c r="P124" s="13" t="n"/>
-      <c r="Q124" s="24" t="n"/>
+      <c r="Q124" s="13" t="n"/>
+      <c r="R124" s="24" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="8" t="n"/>
@@ -7016,7 +7200,8 @@
       <c r="N125" s="9" t="n"/>
       <c r="O125" s="9" t="n"/>
       <c r="P125" s="9" t="n"/>
-      <c r="Q125" s="22" t="n"/>
+      <c r="Q125" s="9" t="n"/>
+      <c r="R125" s="22" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="12" t="n"/>
@@ -7035,7 +7220,8 @@
       <c r="N126" s="13" t="n"/>
       <c r="O126" s="13" t="n"/>
       <c r="P126" s="13" t="n"/>
-      <c r="Q126" s="24" t="n"/>
+      <c r="Q126" s="13" t="n"/>
+      <c r="R126" s="24" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="8" t="n"/>
@@ -7054,7 +7240,8 @@
       <c r="N127" s="9" t="n"/>
       <c r="O127" s="9" t="n"/>
       <c r="P127" s="9" t="n"/>
-      <c r="Q127" s="22" t="n"/>
+      <c r="Q127" s="9" t="n"/>
+      <c r="R127" s="22" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="n"/>
@@ -7073,7 +7260,8 @@
       <c r="N128" s="13" t="n"/>
       <c r="O128" s="13" t="n"/>
       <c r="P128" s="13" t="n"/>
-      <c r="Q128" s="24" t="n"/>
+      <c r="Q128" s="13" t="n"/>
+      <c r="R128" s="24" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="8" t="n"/>
@@ -7092,7 +7280,8 @@
       <c r="N129" s="9" t="n"/>
       <c r="O129" s="9" t="n"/>
       <c r="P129" s="9" t="n"/>
-      <c r="Q129" s="22" t="n"/>
+      <c r="Q129" s="9" t="n"/>
+      <c r="R129" s="22" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="12" t="n"/>
@@ -7111,7 +7300,8 @@
       <c r="N130" s="13" t="n"/>
       <c r="O130" s="13" t="n"/>
       <c r="P130" s="13" t="n"/>
-      <c r="Q130" s="24" t="n"/>
+      <c r="Q130" s="13" t="n"/>
+      <c r="R130" s="24" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="8" t="n"/>
@@ -7130,7 +7320,8 @@
       <c r="N131" s="9" t="n"/>
       <c r="O131" s="9" t="n"/>
       <c r="P131" s="9" t="n"/>
-      <c r="Q131" s="22" t="n"/>
+      <c r="Q131" s="9" t="n"/>
+      <c r="R131" s="22" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="12" t="n"/>
@@ -7149,7 +7340,8 @@
       <c r="N132" s="13" t="n"/>
       <c r="O132" s="13" t="n"/>
       <c r="P132" s="13" t="n"/>
-      <c r="Q132" s="24" t="n"/>
+      <c r="Q132" s="13" t="n"/>
+      <c r="R132" s="24" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="8" t="n"/>
@@ -7168,7 +7360,8 @@
       <c r="N133" s="9" t="n"/>
       <c r="O133" s="9" t="n"/>
       <c r="P133" s="9" t="n"/>
-      <c r="Q133" s="22" t="n"/>
+      <c r="Q133" s="9" t="n"/>
+      <c r="R133" s="22" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="12" t="n"/>
@@ -7187,7 +7380,8 @@
       <c r="N134" s="13" t="n"/>
       <c r="O134" s="13" t="n"/>
       <c r="P134" s="13" t="n"/>
-      <c r="Q134" s="24" t="n"/>
+      <c r="Q134" s="13" t="n"/>
+      <c r="R134" s="24" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="8" t="n"/>
@@ -7206,7 +7400,8 @@
       <c r="N135" s="9" t="n"/>
       <c r="O135" s="9" t="n"/>
       <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="22" t="n"/>
+      <c r="Q135" s="9" t="n"/>
+      <c r="R135" s="22" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="12" t="n"/>
@@ -7225,7 +7420,8 @@
       <c r="N136" s="13" t="n"/>
       <c r="O136" s="13" t="n"/>
       <c r="P136" s="13" t="n"/>
-      <c r="Q136" s="24" t="n"/>
+      <c r="Q136" s="13" t="n"/>
+      <c r="R136" s="24" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="8" t="n"/>
@@ -7244,7 +7440,8 @@
       <c r="N137" s="9" t="n"/>
       <c r="O137" s="9" t="n"/>
       <c r="P137" s="9" t="n"/>
-      <c r="Q137" s="22" t="n"/>
+      <c r="Q137" s="9" t="n"/>
+      <c r="R137" s="22" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="12" t="n"/>
@@ -7263,7 +7460,8 @@
       <c r="N138" s="13" t="n"/>
       <c r="O138" s="13" t="n"/>
       <c r="P138" s="13" t="n"/>
-      <c r="Q138" s="24" t="n"/>
+      <c r="Q138" s="13" t="n"/>
+      <c r="R138" s="24" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="8" t="n"/>
@@ -7282,7 +7480,8 @@
       <c r="N139" s="9" t="n"/>
       <c r="O139" s="9" t="n"/>
       <c r="P139" s="9" t="n"/>
-      <c r="Q139" s="22" t="n"/>
+      <c r="Q139" s="9" t="n"/>
+      <c r="R139" s="22" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="12" t="n"/>
@@ -7301,13 +7500,14 @@
       <c r="N140" s="13" t="n"/>
       <c r="O140" s="13" t="n"/>
       <c r="P140" s="13" t="n"/>
-      <c r="Q140" s="24" t="n"/>
+      <c r="Q140" s="13" t="n"/>
+      <c r="R140" s="24" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -394,6 +394,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -585,8 +603,11 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당자
-(직접 입력)</t>
+        <t>▣ 부서 담당자
+• 부서 내 실제 담당자 이름 입력
+  예: 정민규, 한재운, 이찬
+• 입력 시: PMS에도 자동 반영
+• 빈 칸: 부서 참여 확정, 담당자 미정</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -600,45 +621,78 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성
-(직접 입력)</t>
+        <t>▣ BOM작성 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매검토
-(직접 입력)</t>
+        <t>▣ 구매검토 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 발주
-(직접 입력)</t>
+        <t>▣ 발주 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 입고
-(직접 입력)</t>
+        <t>▣ 입고 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주
-입고일
-(직접 입력)</t>
+        <t>▣ 외주 입고일 (양산 외주발주)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD
+• 외부업체에서 양산 가공품이 실제 입고된 날짜
+• 비워두면: 대시보드 외주현황에 '진행중'
+• 입고일 입력 시: '입고완료' 자동 분류</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모
-(직접 입력)</t>
+        <t>▣ 메모 (부서 자유 입력)
+• 자유 텍스트 입력
+• 활용:
+  - 이슈사항 (예: 자재 결품, 외주 지연)
+  - 변경 요청 (예: 사양 변경, 납기 조정)
+  - 다른 부서·PM에게 공유할 정보
+• 대시보드 집계에는 미포함</t>
       </text>
     </comment>
   </commentList>
@@ -959,7 +1013,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -983,7 +1037,7 @@
       <c r="R1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1004,9 +1058,9 @@
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="17" t="n"/>
-      <c r="R2" s="60" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="R2" s="67" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:07</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,12 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -208,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -394,6 +400,39 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -621,7 +660,8 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ BOM작성 (세부항목 진척률)
+        <t>▣ 외주
+발주일 (세부항목 진척률)
 ★ 진척률 % 입력 (날짜 아님 ⚠️)
 • 0~1 사이 소수로 입력
   예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
@@ -632,39 +672,6 @@
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 구매검토 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-      </text>
-    </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 발주 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-      </text>
-    </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 입고 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-      </text>
-    </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
-      <text>
         <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
@@ -673,7 +680,7 @@
 • 입고일 입력 시: '입고완료' 자동 분류</t>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <t>▣ 부서 작업 상태
 • 드롭다운 선택:
@@ -684,7 +691,7 @@
 • 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
@@ -989,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1003,17 +1010,17 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" style="43" min="12" max="12"/>
-    <col width="10" customWidth="1" style="43" min="13" max="13"/>
-    <col width="6" customWidth="1" style="43" min="14" max="14"/>
-    <col width="6" customWidth="1" style="43" min="15" max="15"/>
+    <col width="12" customWidth="1" style="43" min="12" max="12"/>
+    <col width="12" customWidth="1" style="43" min="13" max="13"/>
+    <col width="10" customWidth="1" style="43" min="14" max="14"/>
+    <col width="28" customWidth="1" style="43" min="15" max="15"/>
     <col width="12" customWidth="1" style="43" min="16" max="16"/>
     <col width="10" customWidth="1" style="43" min="17" max="17"/>
     <col width="28" customWidth="1" style="43" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="65" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1031,13 +1038,10 @@
       <c r="L1" s="16" t="n"/>
       <c r="M1" s="16" t="n"/>
       <c r="N1" s="16" t="n"/>
-      <c r="O1" s="16" t="n"/>
-      <c r="P1" s="16" t="n"/>
-      <c r="Q1" s="16" t="n"/>
-      <c r="R1" s="17" t="n"/>
+      <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="66" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1054,13 +1058,10 @@
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
-      <c r="N2" s="16" t="n"/>
-      <c r="O2" s="16" t="n"/>
-      <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="17" t="n"/>
-      <c r="R2" s="67" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:07</t>
+      <c r="N2" s="17" t="n"/>
+      <c r="O2" s="78" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:52</t>
         </is>
       </c>
     </row>
@@ -1120,37 +1121,22 @@
           <t>🔒자동</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>PO후입력</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1212,38 +1198,24 @@
           <t>전체진척률(%)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>BOM작성</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>구매검토</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>발주</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>입고</t>
-        </is>
-      </c>
-      <c r="P4" s="61" t="inlineStr">
+      <c r="L4" s="61" t="inlineStr">
+        <is>
+          <t>외주
+발주일</t>
+        </is>
+      </c>
+      <c r="M4" s="61" t="inlineStr">
         <is>
           <t>외주
 입고일</t>
         </is>
       </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1295,13 +1267,10 @@
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="9" t="n"/>
-      <c r="R5" s="22" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1349,13 +1318,10 @@
       </c>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="14" t="inlineStr"/>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="24" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="13" t="n"/>
+      <c r="O6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1403,13 +1369,10 @@
       </c>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="22" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1457,13 +1420,10 @@
       </c>
       <c r="J8" s="13" t="n"/>
       <c r="K8" s="14" t="inlineStr"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="24" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1511,13 +1471,10 @@
       </c>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="22" t="n"/>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1565,13 +1522,10 @@
       </c>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="14" t="inlineStr"/>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="15" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="24" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1619,13 +1573,10 @@
       </c>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="22" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1673,13 +1624,10 @@
       </c>
       <c r="J12" s="13" t="n"/>
       <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15" t="n"/>
-      <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="13" t="n"/>
-      <c r="R12" s="24" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1727,13 +1675,10 @@
       </c>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="22" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="9" t="n"/>
+      <c r="O13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1781,13 +1726,10 @@
       </c>
       <c r="J14" s="13" t="n"/>
       <c r="K14" s="14" t="inlineStr"/>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="24" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1835,13 +1777,10 @@
       </c>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="22" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1889,13 +1828,10 @@
       </c>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="24" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -1943,13 +1879,10 @@
       </c>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="22" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -1997,13 +1930,10 @@
       </c>
       <c r="J18" s="13" t="n"/>
       <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="24" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2051,13 +1981,10 @@
       </c>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="22" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2105,13 +2032,10 @@
       </c>
       <c r="J20" s="13" t="n"/>
       <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="24" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2159,13 +2083,10 @@
       </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="11" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="22" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2213,13 +2134,10 @@
       </c>
       <c r="J22" s="13" t="n"/>
       <c r="K22" s="14" t="inlineStr"/>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="24" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2267,13 +2185,10 @@
       </c>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="22" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2321,13 +2236,10 @@
       </c>
       <c r="J24" s="13" t="n"/>
       <c r="K24" s="14" t="inlineStr"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="24" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2375,13 +2287,10 @@
       </c>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="11" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="22" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2429,13 +2338,10 @@
       </c>
       <c r="J26" s="13" t="n"/>
       <c r="K26" s="14" t="inlineStr"/>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="24" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2483,13 +2389,10 @@
       </c>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="11" t="n"/>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="22" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n">
@@ -2537,13 +2440,10 @@
       </c>
       <c r="J28" s="13" t="n"/>
       <c r="K28" s="14" t="inlineStr"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="24" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -2591,13 +2491,10 @@
       </c>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="n"/>
-      <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="22" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n">
@@ -2645,13 +2542,10 @@
       </c>
       <c r="J30" s="13" t="n"/>
       <c r="K30" s="14" t="inlineStr"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="13" t="n"/>
-      <c r="R30" s="24" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="13" t="n"/>
+      <c r="O30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -2699,13 +2593,10 @@
       </c>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="22" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="9" t="n"/>
+      <c r="O31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n">
@@ -2753,13 +2644,10 @@
       </c>
       <c r="J32" s="13" t="n"/>
       <c r="K32" s="14" t="inlineStr"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="13" t="n"/>
-      <c r="R32" s="24" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -2807,13 +2695,10 @@
       </c>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-      <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
-      <c r="R33" s="22" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n">
@@ -2861,13 +2746,10 @@
       </c>
       <c r="J34" s="13" t="n"/>
       <c r="K34" s="14" t="inlineStr"/>
-      <c r="L34" s="15" t="n"/>
-      <c r="M34" s="15" t="n"/>
-      <c r="N34" s="15" t="n"/>
-      <c r="O34" s="15" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="24" t="n"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="13" t="n"/>
+      <c r="N34" s="13" t="n"/>
+      <c r="O34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -2915,13 +2797,10 @@
       </c>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="11" t="n"/>
-      <c r="O35" s="11" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="22" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n">
@@ -2969,13 +2848,10 @@
       </c>
       <c r="J36" s="13" t="n"/>
       <c r="K36" s="14" t="inlineStr"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
-      <c r="N36" s="15" t="n"/>
-      <c r="O36" s="15" t="n"/>
-      <c r="P36" s="13" t="n"/>
-      <c r="Q36" s="13" t="n"/>
-      <c r="R36" s="24" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="13" t="n"/>
+      <c r="N36" s="13" t="n"/>
+      <c r="O36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -3023,13 +2899,10 @@
       </c>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="11" t="n"/>
-      <c r="O37" s="11" t="n"/>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="22" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n">
@@ -3077,13 +2950,10 @@
       </c>
       <c r="J38" s="13" t="n"/>
       <c r="K38" s="14" t="inlineStr"/>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="15" t="n"/>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="15" t="n"/>
-      <c r="P38" s="13" t="n"/>
-      <c r="Q38" s="13" t="n"/>
-      <c r="R38" s="24" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -3131,13 +3001,10 @@
       </c>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="11" t="n"/>
-      <c r="M39" s="11" t="n"/>
-      <c r="N39" s="11" t="n"/>
-      <c r="O39" s="11" t="n"/>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="22" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n">
@@ -3185,13 +3052,10 @@
       </c>
       <c r="J40" s="13" t="n"/>
       <c r="K40" s="14" t="inlineStr"/>
-      <c r="L40" s="15" t="n"/>
-      <c r="M40" s="15" t="n"/>
-      <c r="N40" s="15" t="n"/>
-      <c r="O40" s="15" t="n"/>
-      <c r="P40" s="13" t="n"/>
-      <c r="Q40" s="13" t="n"/>
-      <c r="R40" s="24" t="n"/>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="13" t="n"/>
+      <c r="N40" s="13" t="n"/>
+      <c r="O40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -3239,13 +3103,10 @@
       </c>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="11" t="n"/>
-      <c r="N41" s="11" t="n"/>
-      <c r="O41" s="11" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="22" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n">
@@ -3293,13 +3154,10 @@
       </c>
       <c r="J42" s="13" t="n"/>
       <c r="K42" s="14" t="inlineStr"/>
-      <c r="L42" s="15" t="n"/>
-      <c r="M42" s="15" t="n"/>
-      <c r="N42" s="15" t="n"/>
-      <c r="O42" s="15" t="n"/>
-      <c r="P42" s="13" t="n"/>
-      <c r="Q42" s="13" t="n"/>
-      <c r="R42" s="24" t="n"/>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="13" t="n"/>
+      <c r="N42" s="13" t="n"/>
+      <c r="O42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -3347,13 +3205,10 @@
       </c>
       <c r="J43" s="9" t="n"/>
       <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="11" t="n"/>
-      <c r="N43" s="11" t="n"/>
-      <c r="O43" s="11" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="22" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n">
@@ -3401,13 +3256,10 @@
       </c>
       <c r="J44" s="13" t="n"/>
       <c r="K44" s="14" t="inlineStr"/>
-      <c r="L44" s="15" t="n"/>
-      <c r="M44" s="15" t="n"/>
-      <c r="N44" s="15" t="n"/>
-      <c r="O44" s="15" t="n"/>
-      <c r="P44" s="13" t="n"/>
-      <c r="Q44" s="13" t="n"/>
-      <c r="R44" s="24" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="13" t="n"/>
+      <c r="N44" s="13" t="n"/>
+      <c r="O44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -3455,13 +3307,10 @@
       </c>
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="11" t="n"/>
-      <c r="M45" s="11" t="n"/>
-      <c r="N45" s="11" t="n"/>
-      <c r="O45" s="11" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
-      <c r="R45" s="22" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n">
@@ -3509,13 +3358,10 @@
       </c>
       <c r="J46" s="13" t="n"/>
       <c r="K46" s="14" t="inlineStr"/>
-      <c r="L46" s="15" t="n"/>
-      <c r="M46" s="15" t="n"/>
-      <c r="N46" s="15" t="n"/>
-      <c r="O46" s="15" t="n"/>
-      <c r="P46" s="13" t="n"/>
-      <c r="Q46" s="13" t="n"/>
-      <c r="R46" s="24" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
+      <c r="N46" s="13" t="n"/>
+      <c r="O46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -3563,13 +3409,10 @@
       </c>
       <c r="J47" s="9" t="n"/>
       <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="11" t="n"/>
-      <c r="M47" s="11" t="n"/>
-      <c r="N47" s="11" t="n"/>
-      <c r="O47" s="11" t="n"/>
-      <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
-      <c r="R47" s="22" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n">
@@ -3617,13 +3460,10 @@
       </c>
       <c r="J48" s="13" t="n"/>
       <c r="K48" s="14" t="inlineStr"/>
-      <c r="L48" s="15" t="n"/>
-      <c r="M48" s="15" t="n"/>
-      <c r="N48" s="15" t="n"/>
-      <c r="O48" s="15" t="n"/>
-      <c r="P48" s="13" t="n"/>
-      <c r="Q48" s="13" t="n"/>
-      <c r="R48" s="24" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="13" t="n"/>
+      <c r="N48" s="13" t="n"/>
+      <c r="O48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -3671,13 +3511,10 @@
       </c>
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="11" t="n"/>
-      <c r="M49" s="11" t="n"/>
-      <c r="N49" s="11" t="n"/>
-      <c r="O49" s="11" t="n"/>
-      <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
-      <c r="R49" s="22" t="n"/>
+      <c r="L49" s="9" t="n"/>
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="9" t="n"/>
+      <c r="O49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n">
@@ -3725,13 +3562,10 @@
       </c>
       <c r="J50" s="13" t="n"/>
       <c r="K50" s="14" t="inlineStr"/>
-      <c r="L50" s="15" t="n"/>
-      <c r="M50" s="15" t="n"/>
-      <c r="N50" s="15" t="n"/>
-      <c r="O50" s="15" t="n"/>
-      <c r="P50" s="13" t="n"/>
-      <c r="Q50" s="13" t="n"/>
-      <c r="R50" s="24" t="n"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="13" t="n"/>
+      <c r="N50" s="13" t="n"/>
+      <c r="O50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -3779,13 +3613,10 @@
       </c>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="11" t="n"/>
-      <c r="O51" s="11" t="n"/>
-      <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
-      <c r="R51" s="22" t="n"/>
+      <c r="L51" s="9" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="9" t="n"/>
+      <c r="O51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -3833,13 +3664,10 @@
       </c>
       <c r="J52" s="13" t="n"/>
       <c r="K52" s="14" t="inlineStr"/>
-      <c r="L52" s="15" t="n"/>
-      <c r="M52" s="15" t="n"/>
-      <c r="N52" s="15" t="n"/>
-      <c r="O52" s="15" t="n"/>
-      <c r="P52" s="13" t="n"/>
-      <c r="Q52" s="13" t="n"/>
-      <c r="R52" s="24" t="n"/>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="13" t="n"/>
+      <c r="N52" s="13" t="n"/>
+      <c r="O52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -3887,13 +3715,10 @@
       </c>
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="11" t="n"/>
-      <c r="M53" s="11" t="n"/>
-      <c r="N53" s="11" t="n"/>
-      <c r="O53" s="11" t="n"/>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
-      <c r="R53" s="22" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n">
@@ -3941,13 +3766,10 @@
       </c>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="14" t="inlineStr"/>
-      <c r="L54" s="15" t="n"/>
-      <c r="M54" s="15" t="n"/>
-      <c r="N54" s="15" t="n"/>
-      <c r="O54" s="15" t="n"/>
-      <c r="P54" s="13" t="n"/>
-      <c r="Q54" s="13" t="n"/>
-      <c r="R54" s="24" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="13" t="n"/>
+      <c r="O54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -3995,13 +3817,10 @@
       </c>
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="11" t="n"/>
-      <c r="N55" s="11" t="n"/>
-      <c r="O55" s="11" t="n"/>
-      <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="9" t="n"/>
-      <c r="R55" s="22" t="n"/>
+      <c r="L55" s="9" t="n"/>
+      <c r="M55" s="9" t="n"/>
+      <c r="N55" s="9" t="n"/>
+      <c r="O55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n">
@@ -4049,13 +3868,10 @@
       </c>
       <c r="J56" s="13" t="n"/>
       <c r="K56" s="14" t="inlineStr"/>
-      <c r="L56" s="15" t="n"/>
-      <c r="M56" s="15" t="n"/>
-      <c r="N56" s="15" t="n"/>
-      <c r="O56" s="15" t="n"/>
-      <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="13" t="n"/>
-      <c r="R56" s="24" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="13" t="n"/>
+      <c r="N56" s="13" t="n"/>
+      <c r="O56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -4103,13 +3919,10 @@
       </c>
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="11" t="n"/>
-      <c r="M57" s="11" t="n"/>
-      <c r="N57" s="11" t="n"/>
-      <c r="O57" s="11" t="n"/>
-      <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="9" t="n"/>
-      <c r="R57" s="22" t="n"/>
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="9" t="n"/>
+      <c r="O57" s="22" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -4157,13 +3970,10 @@
       </c>
       <c r="J58" s="13" t="n"/>
       <c r="K58" s="14" t="inlineStr"/>
-      <c r="L58" s="15" t="n"/>
-      <c r="M58" s="15" t="n"/>
-      <c r="N58" s="15" t="n"/>
-      <c r="O58" s="15" t="n"/>
-      <c r="P58" s="13" t="n"/>
-      <c r="Q58" s="13" t="n"/>
-      <c r="R58" s="24" t="n"/>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="13" t="n"/>
+      <c r="N58" s="13" t="n"/>
+      <c r="O58" s="24" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -4211,13 +4021,10 @@
       </c>
       <c r="J59" s="9" t="n"/>
       <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="11" t="n"/>
-      <c r="M59" s="11" t="n"/>
-      <c r="N59" s="11" t="n"/>
-      <c r="O59" s="11" t="n"/>
-      <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="9" t="n"/>
-      <c r="R59" s="22" t="n"/>
+      <c r="L59" s="9" t="n"/>
+      <c r="M59" s="9" t="n"/>
+      <c r="N59" s="9" t="n"/>
+      <c r="O59" s="22" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="12" t="n">
@@ -4265,13 +4072,10 @@
       </c>
       <c r="J60" s="13" t="n"/>
       <c r="K60" s="14" t="inlineStr"/>
-      <c r="L60" s="15" t="n"/>
-      <c r="M60" s="15" t="n"/>
-      <c r="N60" s="15" t="n"/>
-      <c r="O60" s="15" t="n"/>
-      <c r="P60" s="13" t="n"/>
-      <c r="Q60" s="13" t="n"/>
-      <c r="R60" s="24" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="13" t="n"/>
+      <c r="N60" s="13" t="n"/>
+      <c r="O60" s="24" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -4319,13 +4123,10 @@
       </c>
       <c r="J61" s="9" t="n"/>
       <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="11" t="n"/>
-      <c r="M61" s="11" t="n"/>
-      <c r="N61" s="11" t="n"/>
-      <c r="O61" s="11" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="9" t="n"/>
-      <c r="R61" s="22" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="22" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="12" t="n">
@@ -4373,13 +4174,10 @@
       </c>
       <c r="J62" s="13" t="n"/>
       <c r="K62" s="14" t="inlineStr"/>
-      <c r="L62" s="15" t="n"/>
-      <c r="M62" s="15" t="n"/>
-      <c r="N62" s="15" t="n"/>
-      <c r="O62" s="15" t="n"/>
-      <c r="P62" s="13" t="n"/>
-      <c r="Q62" s="13" t="n"/>
-      <c r="R62" s="24" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="13" t="n"/>
+      <c r="N62" s="13" t="n"/>
+      <c r="O62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -4427,13 +4225,10 @@
       </c>
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="11" t="n"/>
-      <c r="M63" s="11" t="n"/>
-      <c r="N63" s="11" t="n"/>
-      <c r="O63" s="11" t="n"/>
-      <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="9" t="n"/>
-      <c r="R63" s="22" t="n"/>
+      <c r="L63" s="9" t="n"/>
+      <c r="M63" s="9" t="n"/>
+      <c r="N63" s="9" t="n"/>
+      <c r="O63" s="22" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="12" t="n">
@@ -4481,13 +4276,10 @@
       </c>
       <c r="J64" s="13" t="n"/>
       <c r="K64" s="14" t="inlineStr"/>
-      <c r="L64" s="15" t="n"/>
-      <c r="M64" s="15" t="n"/>
-      <c r="N64" s="15" t="n"/>
-      <c r="O64" s="15" t="n"/>
-      <c r="P64" s="13" t="n"/>
-      <c r="Q64" s="13" t="n"/>
-      <c r="R64" s="24" t="n"/>
+      <c r="L64" s="13" t="n"/>
+      <c r="M64" s="13" t="n"/>
+      <c r="N64" s="13" t="n"/>
+      <c r="O64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="8" t="n">
@@ -4535,13 +4327,10 @@
       </c>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="11" t="n"/>
-      <c r="M65" s="11" t="n"/>
-      <c r="N65" s="11" t="n"/>
-      <c r="O65" s="11" t="n"/>
-      <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="9" t="n"/>
-      <c r="R65" s="22" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="22" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="12" t="n">
@@ -4589,13 +4378,10 @@
       </c>
       <c r="J66" s="13" t="n"/>
       <c r="K66" s="14" t="inlineStr"/>
-      <c r="L66" s="15" t="n"/>
-      <c r="M66" s="15" t="n"/>
-      <c r="N66" s="15" t="n"/>
-      <c r="O66" s="15" t="n"/>
-      <c r="P66" s="13" t="n"/>
-      <c r="Q66" s="13" t="n"/>
-      <c r="R66" s="24" t="n"/>
+      <c r="L66" s="13" t="n"/>
+      <c r="M66" s="13" t="n"/>
+      <c r="N66" s="13" t="n"/>
+      <c r="O66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="8" t="n">
@@ -4643,13 +4429,10 @@
       </c>
       <c r="J67" s="9" t="n"/>
       <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="11" t="n"/>
-      <c r="M67" s="11" t="n"/>
-      <c r="N67" s="11" t="n"/>
-      <c r="O67" s="11" t="n"/>
-      <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="9" t="n"/>
-      <c r="R67" s="22" t="n"/>
+      <c r="L67" s="9" t="n"/>
+      <c r="M67" s="9" t="n"/>
+      <c r="N67" s="9" t="n"/>
+      <c r="O67" s="22" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="12" t="n">
@@ -4697,13 +4480,10 @@
       </c>
       <c r="J68" s="13" t="n"/>
       <c r="K68" s="14" t="inlineStr"/>
-      <c r="L68" s="15" t="n"/>
-      <c r="M68" s="15" t="n"/>
-      <c r="N68" s="15" t="n"/>
-      <c r="O68" s="15" t="n"/>
-      <c r="P68" s="13" t="n"/>
-      <c r="Q68" s="13" t="n"/>
-      <c r="R68" s="24" t="n"/>
+      <c r="L68" s="13" t="n"/>
+      <c r="M68" s="13" t="n"/>
+      <c r="N68" s="13" t="n"/>
+      <c r="O68" s="24" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="8" t="n">
@@ -4751,13 +4531,10 @@
       </c>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="11" t="n"/>
-      <c r="M69" s="11" t="n"/>
-      <c r="N69" s="11" t="n"/>
-      <c r="O69" s="11" t="n"/>
-      <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="9" t="n"/>
-      <c r="R69" s="22" t="n"/>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="9" t="n"/>
+      <c r="O69" s="22" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="12" t="n">
@@ -4805,13 +4582,10 @@
       </c>
       <c r="J70" s="13" t="n"/>
       <c r="K70" s="14" t="inlineStr"/>
-      <c r="L70" s="15" t="n"/>
-      <c r="M70" s="15" t="n"/>
-      <c r="N70" s="15" t="n"/>
-      <c r="O70" s="15" t="n"/>
-      <c r="P70" s="13" t="n"/>
-      <c r="Q70" s="13" t="n"/>
-      <c r="R70" s="24" t="n"/>
+      <c r="L70" s="13" t="n"/>
+      <c r="M70" s="13" t="n"/>
+      <c r="N70" s="13" t="n"/>
+      <c r="O70" s="24" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="8" t="n">
@@ -4859,13 +4633,10 @@
       </c>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="11" t="n"/>
-      <c r="M71" s="11" t="n"/>
-      <c r="N71" s="11" t="n"/>
-      <c r="O71" s="11" t="n"/>
-      <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="9" t="n"/>
-      <c r="R71" s="22" t="n"/>
+      <c r="L71" s="9" t="n"/>
+      <c r="M71" s="9" t="n"/>
+      <c r="N71" s="9" t="n"/>
+      <c r="O71" s="22" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="12" t="n">
@@ -4913,13 +4684,10 @@
       </c>
       <c r="J72" s="13" t="n"/>
       <c r="K72" s="14" t="inlineStr"/>
-      <c r="L72" s="15" t="n"/>
-      <c r="M72" s="15" t="n"/>
-      <c r="N72" s="15" t="n"/>
-      <c r="O72" s="15" t="n"/>
-      <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="13" t="n"/>
-      <c r="R72" s="24" t="n"/>
+      <c r="L72" s="13" t="n"/>
+      <c r="M72" s="13" t="n"/>
+      <c r="N72" s="13" t="n"/>
+      <c r="O72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="8" t="n">
@@ -4967,13 +4735,10 @@
       </c>
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="11" t="n"/>
-      <c r="M73" s="11" t="n"/>
-      <c r="N73" s="11" t="n"/>
-      <c r="O73" s="11" t="n"/>
-      <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="9" t="n"/>
-      <c r="R73" s="22" t="n"/>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="9" t="n"/>
+      <c r="N73" s="9" t="n"/>
+      <c r="O73" s="22" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="12" t="n">
@@ -5021,13 +4786,10 @@
       </c>
       <c r="J74" s="13" t="n"/>
       <c r="K74" s="14" t="inlineStr"/>
-      <c r="L74" s="15" t="n"/>
-      <c r="M74" s="15" t="n"/>
-      <c r="N74" s="15" t="n"/>
-      <c r="O74" s="15" t="n"/>
-      <c r="P74" s="13" t="n"/>
-      <c r="Q74" s="13" t="n"/>
-      <c r="R74" s="24" t="n"/>
+      <c r="L74" s="13" t="n"/>
+      <c r="M74" s="13" t="n"/>
+      <c r="N74" s="13" t="n"/>
+      <c r="O74" s="24" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="n">
@@ -5075,13 +4837,10 @@
       </c>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="11" t="n"/>
-      <c r="M75" s="11" t="n"/>
-      <c r="N75" s="11" t="n"/>
-      <c r="O75" s="11" t="n"/>
-      <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="9" t="n"/>
-      <c r="R75" s="22" t="n"/>
+      <c r="L75" s="9" t="n"/>
+      <c r="M75" s="9" t="n"/>
+      <c r="N75" s="9" t="n"/>
+      <c r="O75" s="22" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="12" t="n">
@@ -5129,13 +4888,10 @@
       </c>
       <c r="J76" s="13" t="n"/>
       <c r="K76" s="14" t="inlineStr"/>
-      <c r="L76" s="15" t="n"/>
-      <c r="M76" s="15" t="n"/>
-      <c r="N76" s="15" t="n"/>
-      <c r="O76" s="15" t="n"/>
-      <c r="P76" s="13" t="n"/>
-      <c r="Q76" s="13" t="n"/>
-      <c r="R76" s="24" t="n"/>
+      <c r="L76" s="13" t="n"/>
+      <c r="M76" s="13" t="n"/>
+      <c r="N76" s="13" t="n"/>
+      <c r="O76" s="24" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="8" t="n">
@@ -5183,13 +4939,10 @@
       </c>
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
-      <c r="O77" s="11" t="n"/>
-      <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="9" t="n"/>
-      <c r="R77" s="22" t="n"/>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="9" t="n"/>
+      <c r="N77" s="9" t="n"/>
+      <c r="O77" s="22" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="12" t="n">
@@ -5237,13 +4990,10 @@
       </c>
       <c r="J78" s="13" t="n"/>
       <c r="K78" s="14" t="inlineStr"/>
-      <c r="L78" s="15" t="n"/>
-      <c r="M78" s="15" t="n"/>
-      <c r="N78" s="15" t="n"/>
-      <c r="O78" s="15" t="n"/>
-      <c r="P78" s="13" t="n"/>
-      <c r="Q78" s="13" t="n"/>
-      <c r="R78" s="24" t="n"/>
+      <c r="L78" s="13" t="n"/>
+      <c r="M78" s="13" t="n"/>
+      <c r="N78" s="13" t="n"/>
+      <c r="O78" s="24" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="8" t="n">
@@ -5291,13 +5041,10 @@
       </c>
       <c r="J79" s="9" t="n"/>
       <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n"/>
-      <c r="O79" s="11" t="n"/>
-      <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="9" t="n"/>
-      <c r="R79" s="22" t="n"/>
+      <c r="L79" s="9" t="n"/>
+      <c r="M79" s="9" t="n"/>
+      <c r="N79" s="9" t="n"/>
+      <c r="O79" s="22" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="12" t="n">
@@ -5345,13 +5092,10 @@
       </c>
       <c r="J80" s="13" t="n"/>
       <c r="K80" s="14" t="inlineStr"/>
-      <c r="L80" s="15" t="n"/>
-      <c r="M80" s="15" t="n"/>
-      <c r="N80" s="15" t="n"/>
-      <c r="O80" s="15" t="n"/>
-      <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="13" t="n"/>
-      <c r="R80" s="24" t="n"/>
+      <c r="L80" s="13" t="n"/>
+      <c r="M80" s="13" t="n"/>
+      <c r="N80" s="13" t="n"/>
+      <c r="O80" s="24" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="8" t="n">
@@ -5399,13 +5143,10 @@
       </c>
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
-      <c r="O81" s="11" t="n"/>
-      <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="9" t="n"/>
-      <c r="R81" s="22" t="n"/>
+      <c r="L81" s="9" t="n"/>
+      <c r="M81" s="9" t="n"/>
+      <c r="N81" s="9" t="n"/>
+      <c r="O81" s="22" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="12" t="n">
@@ -5453,13 +5194,10 @@
       </c>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="14" t="inlineStr"/>
-      <c r="L82" s="15" t="n"/>
-      <c r="M82" s="15" t="n"/>
-      <c r="N82" s="15" t="n"/>
-      <c r="O82" s="15" t="n"/>
-      <c r="P82" s="13" t="n"/>
-      <c r="Q82" s="13" t="n"/>
-      <c r="R82" s="24" t="n"/>
+      <c r="L82" s="13" t="n"/>
+      <c r="M82" s="13" t="n"/>
+      <c r="N82" s="13" t="n"/>
+      <c r="O82" s="24" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="8" t="n">
@@ -5507,13 +5245,10 @@
       </c>
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n"/>
-      <c r="O83" s="11" t="n"/>
-      <c r="P83" s="9" t="n"/>
-      <c r="Q83" s="9" t="n"/>
-      <c r="R83" s="22" t="n"/>
+      <c r="L83" s="9" t="n"/>
+      <c r="M83" s="9" t="n"/>
+      <c r="N83" s="9" t="n"/>
+      <c r="O83" s="22" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -5561,13 +5296,10 @@
       </c>
       <c r="J84" s="13" t="n"/>
       <c r="K84" s="14" t="inlineStr"/>
-      <c r="L84" s="15" t="n"/>
-      <c r="M84" s="15" t="n"/>
-      <c r="N84" s="15" t="n"/>
-      <c r="O84" s="15" t="n"/>
-      <c r="P84" s="13" t="n"/>
-      <c r="Q84" s="13" t="n"/>
-      <c r="R84" s="24" t="n"/>
+      <c r="L84" s="13" t="n"/>
+      <c r="M84" s="13" t="n"/>
+      <c r="N84" s="13" t="n"/>
+      <c r="O84" s="24" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="8" t="n">
@@ -5615,13 +5347,10 @@
       </c>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="n"/>
-      <c r="O85" s="11" t="n"/>
-      <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="9" t="n"/>
-      <c r="R85" s="22" t="n"/>
+      <c r="L85" s="9" t="n"/>
+      <c r="M85" s="9" t="n"/>
+      <c r="N85" s="9" t="n"/>
+      <c r="O85" s="22" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="12" t="n">
@@ -5669,13 +5398,10 @@
       </c>
       <c r="J86" s="13" t="n"/>
       <c r="K86" s="14" t="inlineStr"/>
-      <c r="L86" s="15" t="n"/>
-      <c r="M86" s="15" t="n"/>
-      <c r="N86" s="15" t="n"/>
-      <c r="O86" s="15" t="n"/>
-      <c r="P86" s="13" t="n"/>
-      <c r="Q86" s="13" t="n"/>
-      <c r="R86" s="24" t="n"/>
+      <c r="L86" s="13" t="n"/>
+      <c r="M86" s="13" t="n"/>
+      <c r="N86" s="13" t="n"/>
+      <c r="O86" s="24" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -5723,13 +5449,10 @@
       </c>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="11" t="n"/>
-      <c r="M87" s="11" t="n"/>
-      <c r="N87" s="11" t="n"/>
-      <c r="O87" s="11" t="n"/>
-      <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="9" t="n"/>
-      <c r="R87" s="22" t="n"/>
+      <c r="L87" s="9" t="n"/>
+      <c r="M87" s="9" t="n"/>
+      <c r="N87" s="9" t="n"/>
+      <c r="O87" s="22" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="12" t="n">
@@ -5777,13 +5500,10 @@
       </c>
       <c r="J88" s="13" t="n"/>
       <c r="K88" s="14" t="inlineStr"/>
-      <c r="L88" s="15" t="n"/>
-      <c r="M88" s="15" t="n"/>
-      <c r="N88" s="15" t="n"/>
-      <c r="O88" s="15" t="n"/>
-      <c r="P88" s="13" t="n"/>
-      <c r="Q88" s="13" t="n"/>
-      <c r="R88" s="24" t="n"/>
+      <c r="L88" s="13" t="n"/>
+      <c r="M88" s="13" t="n"/>
+      <c r="N88" s="13" t="n"/>
+      <c r="O88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="8" t="n">
@@ -5831,13 +5551,10 @@
       </c>
       <c r="J89" s="9" t="n"/>
       <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="11" t="n"/>
-      <c r="M89" s="11" t="n"/>
-      <c r="N89" s="11" t="n"/>
-      <c r="O89" s="11" t="n"/>
-      <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="9" t="n"/>
-      <c r="R89" s="22" t="n"/>
+      <c r="L89" s="9" t="n"/>
+      <c r="M89" s="9" t="n"/>
+      <c r="N89" s="9" t="n"/>
+      <c r="O89" s="22" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="12" t="n">
@@ -5885,13 +5602,10 @@
       </c>
       <c r="J90" s="13" t="n"/>
       <c r="K90" s="14" t="inlineStr"/>
-      <c r="L90" s="15" t="n"/>
-      <c r="M90" s="15" t="n"/>
-      <c r="N90" s="15" t="n"/>
-      <c r="O90" s="15" t="n"/>
-      <c r="P90" s="13" t="n"/>
-      <c r="Q90" s="13" t="n"/>
-      <c r="R90" s="24" t="n"/>
+      <c r="L90" s="13" t="n"/>
+      <c r="M90" s="13" t="n"/>
+      <c r="N90" s="13" t="n"/>
+      <c r="O90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="8" t="n">
@@ -5939,13 +5653,10 @@
       </c>
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="10" t="inlineStr"/>
-      <c r="L91" s="11" t="n"/>
-      <c r="M91" s="11" t="n"/>
-      <c r="N91" s="11" t="n"/>
-      <c r="O91" s="11" t="n"/>
-      <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="9" t="n"/>
-      <c r="R91" s="22" t="n"/>
+      <c r="L91" s="9" t="n"/>
+      <c r="M91" s="9" t="n"/>
+      <c r="N91" s="9" t="n"/>
+      <c r="O91" s="22" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="12" t="n">
@@ -5993,13 +5704,10 @@
       </c>
       <c r="J92" s="13" t="n"/>
       <c r="K92" s="14" t="inlineStr"/>
-      <c r="L92" s="15" t="n"/>
-      <c r="M92" s="15" t="n"/>
-      <c r="N92" s="15" t="n"/>
-      <c r="O92" s="15" t="n"/>
-      <c r="P92" s="13" t="n"/>
-      <c r="Q92" s="13" t="n"/>
-      <c r="R92" s="24" t="n"/>
+      <c r="L92" s="13" t="n"/>
+      <c r="M92" s="13" t="n"/>
+      <c r="N92" s="13" t="n"/>
+      <c r="O92" s="24" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="8" t="n">
@@ -6047,13 +5755,10 @@
       </c>
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="11" t="n"/>
-      <c r="M93" s="11" t="n"/>
-      <c r="N93" s="11" t="n"/>
-      <c r="O93" s="11" t="n"/>
-      <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="9" t="n"/>
-      <c r="R93" s="22" t="n"/>
+      <c r="L93" s="9" t="n"/>
+      <c r="M93" s="9" t="n"/>
+      <c r="N93" s="9" t="n"/>
+      <c r="O93" s="22" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="12" t="n">
@@ -6101,13 +5806,10 @@
       </c>
       <c r="J94" s="13" t="n"/>
       <c r="K94" s="14" t="inlineStr"/>
-      <c r="L94" s="15" t="n"/>
-      <c r="M94" s="15" t="n"/>
-      <c r="N94" s="15" t="n"/>
-      <c r="O94" s="15" t="n"/>
-      <c r="P94" s="13" t="n"/>
-      <c r="Q94" s="13" t="n"/>
-      <c r="R94" s="24" t="n"/>
+      <c r="L94" s="13" t="n"/>
+      <c r="M94" s="13" t="n"/>
+      <c r="N94" s="13" t="n"/>
+      <c r="O94" s="24" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="8" t="n">
@@ -6155,13 +5857,10 @@
       </c>
       <c r="J95" s="9" t="n"/>
       <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="11" t="n"/>
-      <c r="M95" s="11" t="n"/>
-      <c r="N95" s="11" t="n"/>
-      <c r="O95" s="11" t="n"/>
-      <c r="P95" s="9" t="n"/>
-      <c r="Q95" s="9" t="n"/>
-      <c r="R95" s="22" t="n"/>
+      <c r="L95" s="9" t="n"/>
+      <c r="M95" s="9" t="n"/>
+      <c r="N95" s="9" t="n"/>
+      <c r="O95" s="22" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="n">
@@ -6209,13 +5908,10 @@
       </c>
       <c r="J96" s="13" t="n"/>
       <c r="K96" s="14" t="inlineStr"/>
-      <c r="L96" s="15" t="n"/>
-      <c r="M96" s="15" t="n"/>
-      <c r="N96" s="15" t="n"/>
-      <c r="O96" s="15" t="n"/>
-      <c r="P96" s="13" t="n"/>
-      <c r="Q96" s="13" t="n"/>
-      <c r="R96" s="24" t="n"/>
+      <c r="L96" s="13" t="n"/>
+      <c r="M96" s="13" t="n"/>
+      <c r="N96" s="13" t="n"/>
+      <c r="O96" s="24" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="8" t="n">
@@ -6263,13 +5959,10 @@
       </c>
       <c r="J97" s="9" t="n"/>
       <c r="K97" s="10" t="inlineStr"/>
-      <c r="L97" s="11" t="n"/>
-      <c r="M97" s="11" t="n"/>
-      <c r="N97" s="11" t="n"/>
-      <c r="O97" s="11" t="n"/>
-      <c r="P97" s="9" t="n"/>
-      <c r="Q97" s="9" t="n"/>
-      <c r="R97" s="22" t="n"/>
+      <c r="L97" s="9" t="n"/>
+      <c r="M97" s="9" t="n"/>
+      <c r="N97" s="9" t="n"/>
+      <c r="O97" s="22" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="n">
@@ -6317,13 +6010,10 @@
       </c>
       <c r="J98" s="13" t="n"/>
       <c r="K98" s="14" t="inlineStr"/>
-      <c r="L98" s="15" t="n"/>
-      <c r="M98" s="15" t="n"/>
-      <c r="N98" s="15" t="n"/>
-      <c r="O98" s="15" t="n"/>
-      <c r="P98" s="13" t="n"/>
-      <c r="Q98" s="13" t="n"/>
-      <c r="R98" s="24" t="n"/>
+      <c r="L98" s="13" t="n"/>
+      <c r="M98" s="13" t="n"/>
+      <c r="N98" s="13" t="n"/>
+      <c r="O98" s="24" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -6371,13 +6061,10 @@
       </c>
       <c r="J99" s="9" t="n"/>
       <c r="K99" s="10" t="inlineStr"/>
-      <c r="L99" s="11" t="n"/>
-      <c r="M99" s="11" t="n"/>
-      <c r="N99" s="11" t="n"/>
-      <c r="O99" s="11" t="n"/>
-      <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="9" t="n"/>
-      <c r="R99" s="22" t="n"/>
+      <c r="L99" s="9" t="n"/>
+      <c r="M99" s="9" t="n"/>
+      <c r="N99" s="9" t="n"/>
+      <c r="O99" s="22" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="n">
@@ -6425,13 +6112,10 @@
       </c>
       <c r="J100" s="13" t="n"/>
       <c r="K100" s="14" t="inlineStr"/>
-      <c r="L100" s="15" t="n"/>
-      <c r="M100" s="15" t="n"/>
-      <c r="N100" s="15" t="n"/>
-      <c r="O100" s="15" t="n"/>
-      <c r="P100" s="13" t="n"/>
-      <c r="Q100" s="13" t="n"/>
-      <c r="R100" s="24" t="n"/>
+      <c r="L100" s="13" t="n"/>
+      <c r="M100" s="13" t="n"/>
+      <c r="N100" s="13" t="n"/>
+      <c r="O100" s="24" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="8" t="n">
@@ -6479,13 +6163,10 @@
       </c>
       <c r="J101" s="9" t="n"/>
       <c r="K101" s="10" t="inlineStr"/>
-      <c r="L101" s="11" t="n"/>
-      <c r="M101" s="11" t="n"/>
-      <c r="N101" s="11" t="n"/>
-      <c r="O101" s="11" t="n"/>
-      <c r="P101" s="9" t="n"/>
-      <c r="Q101" s="9" t="n"/>
-      <c r="R101" s="22" t="n"/>
+      <c r="L101" s="9" t="n"/>
+      <c r="M101" s="9" t="n"/>
+      <c r="N101" s="9" t="n"/>
+      <c r="O101" s="22" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="n">
@@ -6533,13 +6214,10 @@
       </c>
       <c r="J102" s="13" t="n"/>
       <c r="K102" s="14" t="inlineStr"/>
-      <c r="L102" s="15" t="n"/>
-      <c r="M102" s="15" t="n"/>
-      <c r="N102" s="15" t="n"/>
-      <c r="O102" s="15" t="n"/>
-      <c r="P102" s="13" t="n"/>
-      <c r="Q102" s="13" t="n"/>
-      <c r="R102" s="24" t="n"/>
+      <c r="L102" s="13" t="n"/>
+      <c r="M102" s="13" t="n"/>
+      <c r="N102" s="13" t="n"/>
+      <c r="O102" s="24" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="8" t="n">
@@ -6587,13 +6265,10 @@
       </c>
       <c r="J103" s="9" t="n"/>
       <c r="K103" s="10" t="inlineStr"/>
-      <c r="L103" s="11" t="n"/>
-      <c r="M103" s="11" t="n"/>
-      <c r="N103" s="11" t="n"/>
-      <c r="O103" s="11" t="n"/>
-      <c r="P103" s="9" t="n"/>
-      <c r="Q103" s="9" t="n"/>
-      <c r="R103" s="22" t="n"/>
+      <c r="L103" s="9" t="n"/>
+      <c r="M103" s="9" t="n"/>
+      <c r="N103" s="9" t="n"/>
+      <c r="O103" s="22" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="n">
@@ -6641,13 +6316,10 @@
       </c>
       <c r="J104" s="13" t="n"/>
       <c r="K104" s="14" t="inlineStr"/>
-      <c r="L104" s="15" t="n"/>
-      <c r="M104" s="15" t="n"/>
-      <c r="N104" s="15" t="n"/>
-      <c r="O104" s="15" t="n"/>
-      <c r="P104" s="13" t="n"/>
-      <c r="Q104" s="13" t="n"/>
-      <c r="R104" s="24" t="n"/>
+      <c r="L104" s="13" t="n"/>
+      <c r="M104" s="13" t="n"/>
+      <c r="N104" s="13" t="n"/>
+      <c r="O104" s="24" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="8" t="n">
@@ -6695,13 +6367,10 @@
       </c>
       <c r="J105" s="9" t="n"/>
       <c r="K105" s="10" t="inlineStr"/>
-      <c r="L105" s="11" t="n"/>
-      <c r="M105" s="11" t="n"/>
-      <c r="N105" s="11" t="n"/>
-      <c r="O105" s="11" t="n"/>
-      <c r="P105" s="9" t="n"/>
-      <c r="Q105" s="9" t="n"/>
-      <c r="R105" s="22" t="n"/>
+      <c r="L105" s="9" t="n"/>
+      <c r="M105" s="9" t="n"/>
+      <c r="N105" s="9" t="n"/>
+      <c r="O105" s="22" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="n">
@@ -6749,13 +6418,10 @@
       </c>
       <c r="J106" s="13" t="n"/>
       <c r="K106" s="14" t="inlineStr"/>
-      <c r="L106" s="15" t="n"/>
-      <c r="M106" s="15" t="n"/>
-      <c r="N106" s="15" t="n"/>
-      <c r="O106" s="15" t="n"/>
-      <c r="P106" s="13" t="n"/>
-      <c r="Q106" s="13" t="n"/>
-      <c r="R106" s="24" t="n"/>
+      <c r="L106" s="13" t="n"/>
+      <c r="M106" s="13" t="n"/>
+      <c r="N106" s="13" t="n"/>
+      <c r="O106" s="24" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -6803,13 +6469,10 @@
       </c>
       <c r="J107" s="9" t="n"/>
       <c r="K107" s="10" t="inlineStr"/>
-      <c r="L107" s="11" t="n"/>
-      <c r="M107" s="11" t="n"/>
-      <c r="N107" s="11" t="n"/>
-      <c r="O107" s="11" t="n"/>
-      <c r="P107" s="9" t="n"/>
-      <c r="Q107" s="9" t="n"/>
-      <c r="R107" s="22" t="n"/>
+      <c r="L107" s="9" t="n"/>
+      <c r="M107" s="9" t="n"/>
+      <c r="N107" s="9" t="n"/>
+      <c r="O107" s="22" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -6857,13 +6520,10 @@
       </c>
       <c r="J108" s="13" t="n"/>
       <c r="K108" s="14" t="inlineStr"/>
-      <c r="L108" s="15" t="n"/>
-      <c r="M108" s="15" t="n"/>
-      <c r="N108" s="15" t="n"/>
-      <c r="O108" s="15" t="n"/>
-      <c r="P108" s="13" t="n"/>
-      <c r="Q108" s="13" t="n"/>
-      <c r="R108" s="24" t="n"/>
+      <c r="L108" s="13" t="n"/>
+      <c r="M108" s="13" t="n"/>
+      <c r="N108" s="13" t="n"/>
+      <c r="O108" s="24" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="8" t="n">
@@ -6910,10 +6570,7 @@
       <c r="L109" s="9" t="n"/>
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
-      <c r="O109" s="9" t="n"/>
-      <c r="P109" s="9" t="n"/>
-      <c r="Q109" s="9" t="n"/>
-      <c r="R109" s="22" t="n"/>
+      <c r="O109" s="22" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="n">
@@ -6952,10 +6609,7 @@
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>
-      <c r="O110" s="13" t="n"/>
-      <c r="P110" s="13" t="n"/>
-      <c r="Q110" s="13" t="n"/>
-      <c r="R110" s="24" t="n"/>
+      <c r="O110" s="24" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="8" t="n"/>
@@ -6972,10 +6626,7 @@
       <c r="L111" s="9" t="n"/>
       <c r="M111" s="9" t="n"/>
       <c r="N111" s="9" t="n"/>
-      <c r="O111" s="9" t="n"/>
-      <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="9" t="n"/>
-      <c r="R111" s="22" t="n"/>
+      <c r="O111" s="22" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="n"/>
@@ -6992,10 +6643,7 @@
       <c r="L112" s="13" t="n"/>
       <c r="M112" s="13" t="n"/>
       <c r="N112" s="13" t="n"/>
-      <c r="O112" s="13" t="n"/>
-      <c r="P112" s="13" t="n"/>
-      <c r="Q112" s="13" t="n"/>
-      <c r="R112" s="24" t="n"/>
+      <c r="O112" s="24" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="8" t="n"/>
@@ -7012,10 +6660,7 @@
       <c r="L113" s="9" t="n"/>
       <c r="M113" s="9" t="n"/>
       <c r="N113" s="9" t="n"/>
-      <c r="O113" s="9" t="n"/>
-      <c r="P113" s="9" t="n"/>
-      <c r="Q113" s="9" t="n"/>
-      <c r="R113" s="22" t="n"/>
+      <c r="O113" s="22" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="n"/>
@@ -7032,10 +6677,7 @@
       <c r="L114" s="13" t="n"/>
       <c r="M114" s="13" t="n"/>
       <c r="N114" s="13" t="n"/>
-      <c r="O114" s="13" t="n"/>
-      <c r="P114" s="13" t="n"/>
-      <c r="Q114" s="13" t="n"/>
-      <c r="R114" s="24" t="n"/>
+      <c r="O114" s="24" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="8" t="n"/>
@@ -7052,10 +6694,7 @@
       <c r="L115" s="9" t="n"/>
       <c r="M115" s="9" t="n"/>
       <c r="N115" s="9" t="n"/>
-      <c r="O115" s="9" t="n"/>
-      <c r="P115" s="9" t="n"/>
-      <c r="Q115" s="9" t="n"/>
-      <c r="R115" s="22" t="n"/>
+      <c r="O115" s="22" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="n"/>
@@ -7072,10 +6711,7 @@
       <c r="L116" s="13" t="n"/>
       <c r="M116" s="13" t="n"/>
       <c r="N116" s="13" t="n"/>
-      <c r="O116" s="13" t="n"/>
-      <c r="P116" s="13" t="n"/>
-      <c r="Q116" s="13" t="n"/>
-      <c r="R116" s="24" t="n"/>
+      <c r="O116" s="24" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="8" t="n"/>
@@ -7092,10 +6728,7 @@
       <c r="L117" s="9" t="n"/>
       <c r="M117" s="9" t="n"/>
       <c r="N117" s="9" t="n"/>
-      <c r="O117" s="9" t="n"/>
-      <c r="P117" s="9" t="n"/>
-      <c r="Q117" s="9" t="n"/>
-      <c r="R117" s="22" t="n"/>
+      <c r="O117" s="22" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="12" t="n"/>
@@ -7112,10 +6745,7 @@
       <c r="L118" s="13" t="n"/>
       <c r="M118" s="13" t="n"/>
       <c r="N118" s="13" t="n"/>
-      <c r="O118" s="13" t="n"/>
-      <c r="P118" s="13" t="n"/>
-      <c r="Q118" s="13" t="n"/>
-      <c r="R118" s="24" t="n"/>
+      <c r="O118" s="24" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="8" t="n"/>
@@ -7132,10 +6762,7 @@
       <c r="L119" s="9" t="n"/>
       <c r="M119" s="9" t="n"/>
       <c r="N119" s="9" t="n"/>
-      <c r="O119" s="9" t="n"/>
-      <c r="P119" s="9" t="n"/>
-      <c r="Q119" s="9" t="n"/>
-      <c r="R119" s="22" t="n"/>
+      <c r="O119" s="22" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="n"/>
@@ -7152,10 +6779,7 @@
       <c r="L120" s="13" t="n"/>
       <c r="M120" s="13" t="n"/>
       <c r="N120" s="13" t="n"/>
-      <c r="O120" s="13" t="n"/>
-      <c r="P120" s="13" t="n"/>
-      <c r="Q120" s="13" t="n"/>
-      <c r="R120" s="24" t="n"/>
+      <c r="O120" s="24" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="8" t="n"/>
@@ -7172,10 +6796,7 @@
       <c r="L121" s="9" t="n"/>
       <c r="M121" s="9" t="n"/>
       <c r="N121" s="9" t="n"/>
-      <c r="O121" s="9" t="n"/>
-      <c r="P121" s="9" t="n"/>
-      <c r="Q121" s="9" t="n"/>
-      <c r="R121" s="22" t="n"/>
+      <c r="O121" s="22" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="n"/>
@@ -7192,10 +6813,7 @@
       <c r="L122" s="13" t="n"/>
       <c r="M122" s="13" t="n"/>
       <c r="N122" s="13" t="n"/>
-      <c r="O122" s="13" t="n"/>
-      <c r="P122" s="13" t="n"/>
-      <c r="Q122" s="13" t="n"/>
-      <c r="R122" s="24" t="n"/>
+      <c r="O122" s="24" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="8" t="n"/>
@@ -7212,10 +6830,7 @@
       <c r="L123" s="9" t="n"/>
       <c r="M123" s="9" t="n"/>
       <c r="N123" s="9" t="n"/>
-      <c r="O123" s="9" t="n"/>
-      <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="9" t="n"/>
-      <c r="R123" s="22" t="n"/>
+      <c r="O123" s="22" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="n"/>
@@ -7232,10 +6847,7 @@
       <c r="L124" s="13" t="n"/>
       <c r="M124" s="13" t="n"/>
       <c r="N124" s="13" t="n"/>
-      <c r="O124" s="13" t="n"/>
-      <c r="P124" s="13" t="n"/>
-      <c r="Q124" s="13" t="n"/>
-      <c r="R124" s="24" t="n"/>
+      <c r="O124" s="24" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="8" t="n"/>
@@ -7252,10 +6864,7 @@
       <c r="L125" s="9" t="n"/>
       <c r="M125" s="9" t="n"/>
       <c r="N125" s="9" t="n"/>
-      <c r="O125" s="9" t="n"/>
-      <c r="P125" s="9" t="n"/>
-      <c r="Q125" s="9" t="n"/>
-      <c r="R125" s="22" t="n"/>
+      <c r="O125" s="22" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="12" t="n"/>
@@ -7272,10 +6881,7 @@
       <c r="L126" s="13" t="n"/>
       <c r="M126" s="13" t="n"/>
       <c r="N126" s="13" t="n"/>
-      <c r="O126" s="13" t="n"/>
-      <c r="P126" s="13" t="n"/>
-      <c r="Q126" s="13" t="n"/>
-      <c r="R126" s="24" t="n"/>
+      <c r="O126" s="24" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="8" t="n"/>
@@ -7292,10 +6898,7 @@
       <c r="L127" s="9" t="n"/>
       <c r="M127" s="9" t="n"/>
       <c r="N127" s="9" t="n"/>
-      <c r="O127" s="9" t="n"/>
-      <c r="P127" s="9" t="n"/>
-      <c r="Q127" s="9" t="n"/>
-      <c r="R127" s="22" t="n"/>
+      <c r="O127" s="22" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="n"/>
@@ -7312,10 +6915,7 @@
       <c r="L128" s="13" t="n"/>
       <c r="M128" s="13" t="n"/>
       <c r="N128" s="13" t="n"/>
-      <c r="O128" s="13" t="n"/>
-      <c r="P128" s="13" t="n"/>
-      <c r="Q128" s="13" t="n"/>
-      <c r="R128" s="24" t="n"/>
+      <c r="O128" s="24" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="8" t="n"/>
@@ -7332,10 +6932,7 @@
       <c r="L129" s="9" t="n"/>
       <c r="M129" s="9" t="n"/>
       <c r="N129" s="9" t="n"/>
-      <c r="O129" s="9" t="n"/>
-      <c r="P129" s="9" t="n"/>
-      <c r="Q129" s="9" t="n"/>
-      <c r="R129" s="22" t="n"/>
+      <c r="O129" s="22" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="12" t="n"/>
@@ -7352,10 +6949,7 @@
       <c r="L130" s="13" t="n"/>
       <c r="M130" s="13" t="n"/>
       <c r="N130" s="13" t="n"/>
-      <c r="O130" s="13" t="n"/>
-      <c r="P130" s="13" t="n"/>
-      <c r="Q130" s="13" t="n"/>
-      <c r="R130" s="24" t="n"/>
+      <c r="O130" s="24" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="8" t="n"/>
@@ -7372,10 +6966,7 @@
       <c r="L131" s="9" t="n"/>
       <c r="M131" s="9" t="n"/>
       <c r="N131" s="9" t="n"/>
-      <c r="O131" s="9" t="n"/>
-      <c r="P131" s="9" t="n"/>
-      <c r="Q131" s="9" t="n"/>
-      <c r="R131" s="22" t="n"/>
+      <c r="O131" s="22" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="12" t="n"/>
@@ -7392,10 +6983,7 @@
       <c r="L132" s="13" t="n"/>
       <c r="M132" s="13" t="n"/>
       <c r="N132" s="13" t="n"/>
-      <c r="O132" s="13" t="n"/>
-      <c r="P132" s="13" t="n"/>
-      <c r="Q132" s="13" t="n"/>
-      <c r="R132" s="24" t="n"/>
+      <c r="O132" s="24" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="8" t="n"/>
@@ -7412,10 +7000,7 @@
       <c r="L133" s="9" t="n"/>
       <c r="M133" s="9" t="n"/>
       <c r="N133" s="9" t="n"/>
-      <c r="O133" s="9" t="n"/>
-      <c r="P133" s="9" t="n"/>
-      <c r="Q133" s="9" t="n"/>
-      <c r="R133" s="22" t="n"/>
+      <c r="O133" s="22" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="12" t="n"/>
@@ -7432,10 +7017,7 @@
       <c r="L134" s="13" t="n"/>
       <c r="M134" s="13" t="n"/>
       <c r="N134" s="13" t="n"/>
-      <c r="O134" s="13" t="n"/>
-      <c r="P134" s="13" t="n"/>
-      <c r="Q134" s="13" t="n"/>
-      <c r="R134" s="24" t="n"/>
+      <c r="O134" s="24" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="8" t="n"/>
@@ -7452,10 +7034,7 @@
       <c r="L135" s="9" t="n"/>
       <c r="M135" s="9" t="n"/>
       <c r="N135" s="9" t="n"/>
-      <c r="O135" s="9" t="n"/>
-      <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="9" t="n"/>
-      <c r="R135" s="22" t="n"/>
+      <c r="O135" s="22" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="12" t="n"/>
@@ -7472,10 +7051,7 @@
       <c r="L136" s="13" t="n"/>
       <c r="M136" s="13" t="n"/>
       <c r="N136" s="13" t="n"/>
-      <c r="O136" s="13" t="n"/>
-      <c r="P136" s="13" t="n"/>
-      <c r="Q136" s="13" t="n"/>
-      <c r="R136" s="24" t="n"/>
+      <c r="O136" s="24" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="8" t="n"/>
@@ -7492,10 +7068,7 @@
       <c r="L137" s="9" t="n"/>
       <c r="M137" s="9" t="n"/>
       <c r="N137" s="9" t="n"/>
-      <c r="O137" s="9" t="n"/>
-      <c r="P137" s="9" t="n"/>
-      <c r="Q137" s="9" t="n"/>
-      <c r="R137" s="22" t="n"/>
+      <c r="O137" s="22" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="12" t="n"/>
@@ -7512,10 +7085,7 @@
       <c r="L138" s="13" t="n"/>
       <c r="M138" s="13" t="n"/>
       <c r="N138" s="13" t="n"/>
-      <c r="O138" s="13" t="n"/>
-      <c r="P138" s="13" t="n"/>
-      <c r="Q138" s="13" t="n"/>
-      <c r="R138" s="24" t="n"/>
+      <c r="O138" s="24" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="8" t="n"/>
@@ -7532,10 +7102,7 @@
       <c r="L139" s="9" t="n"/>
       <c r="M139" s="9" t="n"/>
       <c r="N139" s="9" t="n"/>
-      <c r="O139" s="9" t="n"/>
-      <c r="P139" s="9" t="n"/>
-      <c r="Q139" s="9" t="n"/>
-      <c r="R139" s="22" t="n"/>
+      <c r="O139" s="22" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="12" t="n"/>
@@ -7552,16 +7119,13 @@
       <c r="L140" s="13" t="n"/>
       <c r="M140" s="13" t="n"/>
       <c r="N140" s="13" t="n"/>
-      <c r="O140" s="13" t="n"/>
-      <c r="P140" s="13" t="n"/>
-      <c r="Q140" s="13" t="n"/>
-      <c r="R140" s="24" t="n"/>
+      <c r="O140" s="24" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -424,6 +424,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -660,14 +669,14 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주
-발주일 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        <t>▣ 외주 발주일 (양산 외주발주)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-15
+• 외부업체에 양산 가공품을 ★실제 발주한 날짜★ 기입
+• PO·발주서가 외부업체에 송부된 날짜
+• 외주입고일과 짝 — 발주 후 입고까지 추적
+• 비워두면: 외주 미발주 상태
+• 구매팀 전용 컬럼 (양산 외주 추적)</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
@@ -1020,7 +1029,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1041,7 +1050,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="77" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1059,9 +1068,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="78" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:52</t>
+      <c r="O2" s="81" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -424,6 +424,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -660,11 +669,15 @@
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+• 자동 계산 (수정 불가, sync 시 갱신)
+• 시작일·완료일 입력 기반:
+    0%  = 미착수    (시작일·완료일 모두 빈 칸)
+   50%  = 진행중    (시작일만 입력)
+  100%  = 완료      (완료일까지 입력)
+• ★ 이 값은 '이 부서'만의 진척률입니다.
+• 프로젝트 전체 진척률은 PMS 1_프로젝트등록
+  '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1029,7 +1042,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1050,7 +1063,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="80" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1068,9 +1081,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="O2" s="84" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:44</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1217,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>전체진척률(%)</t>
+          <t>부서진척률(%)</t>
         </is>
       </c>
       <c r="L4" s="61" t="inlineStr">
@@ -1275,7 +1288,9 @@
         </is>
       </c>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
@@ -1326,7 +1341,9 @@
         </is>
       </c>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="14" t="inlineStr"/>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="13" t="n"/>
       <c r="M6" s="13" t="n"/>
       <c r="N6" s="13" t="n"/>
@@ -1377,7 +1394,9 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
@@ -1428,7 +1447,9 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="13" t="n"/>
       <c r="M8" s="13" t="n"/>
       <c r="N8" s="13" t="n"/>
@@ -1479,7 +1500,9 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
@@ -1530,7 +1553,9 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
@@ -1581,7 +1606,9 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
@@ -1632,7 +1659,9 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
       <c r="N12" s="13" t="n"/>
@@ -1683,7 +1712,9 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
@@ -1734,7 +1765,9 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
@@ -1785,7 +1818,9 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
@@ -1836,7 +1871,9 @@
         </is>
       </c>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
@@ -1887,7 +1924,9 @@
         </is>
       </c>
       <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
@@ -1938,7 +1977,9 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="13" t="n"/>
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
@@ -1989,7 +2030,9 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
@@ -2040,7 +2083,9 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="13" t="n"/>
       <c r="M20" s="13" t="n"/>
       <c r="N20" s="13" t="n"/>
@@ -2091,7 +2136,9 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
@@ -2142,7 +2189,9 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="13" t="n"/>
       <c r="M22" s="13" t="n"/>
       <c r="N22" s="13" t="n"/>
@@ -2193,7 +2242,9 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
@@ -2244,7 +2295,9 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="13" t="n"/>
       <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
@@ -2295,7 +2348,9 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
@@ -2346,7 +2401,9 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="13" t="n"/>
       <c r="M26" s="13" t="n"/>
       <c r="N26" s="13" t="n"/>
@@ -2397,7 +2454,9 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
@@ -2448,7 +2507,9 @@
         </is>
       </c>
       <c r="J28" s="13" t="n"/>
-      <c r="K28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" s="13" t="n"/>
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
@@ -2499,7 +2560,9 @@
         </is>
       </c>
       <c r="J29" s="9" t="n"/>
-      <c r="K29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
@@ -2550,7 +2613,9 @@
         </is>
       </c>
       <c r="J30" s="13" t="n"/>
-      <c r="K30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" s="13" t="n"/>
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
@@ -2601,7 +2666,9 @@
         </is>
       </c>
       <c r="J31" s="9" t="n"/>
-      <c r="K31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
@@ -2652,7 +2719,9 @@
         </is>
       </c>
       <c r="J32" s="13" t="n"/>
-      <c r="K32" s="14" t="inlineStr"/>
+      <c r="K32" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" s="13" t="n"/>
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
@@ -2703,7 +2772,9 @@
         </is>
       </c>
       <c r="J33" s="9" t="n"/>
-      <c r="K33" s="10" t="inlineStr"/>
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
@@ -2754,7 +2825,9 @@
         </is>
       </c>
       <c r="J34" s="13" t="n"/>
-      <c r="K34" s="14" t="inlineStr"/>
+      <c r="K34" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L34" s="13" t="n"/>
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
@@ -2805,7 +2878,9 @@
         </is>
       </c>
       <c r="J35" s="9" t="n"/>
-      <c r="K35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
@@ -2856,7 +2931,9 @@
         </is>
       </c>
       <c r="J36" s="13" t="n"/>
-      <c r="K36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L36" s="13" t="n"/>
       <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
@@ -2907,7 +2984,9 @@
         </is>
       </c>
       <c r="J37" s="9" t="n"/>
-      <c r="K37" s="10" t="inlineStr"/>
+      <c r="K37" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
@@ -2958,7 +3037,9 @@
         </is>
       </c>
       <c r="J38" s="13" t="n"/>
-      <c r="K38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="13" t="n"/>
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
@@ -3009,7 +3090,9 @@
         </is>
       </c>
       <c r="J39" s="9" t="n"/>
-      <c r="K39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
@@ -3060,7 +3143,9 @@
         </is>
       </c>
       <c r="J40" s="13" t="n"/>
-      <c r="K40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L40" s="13" t="n"/>
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
@@ -3111,7 +3196,9 @@
         </is>
       </c>
       <c r="J41" s="9" t="n"/>
-      <c r="K41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
@@ -3162,7 +3249,9 @@
         </is>
       </c>
       <c r="J42" s="13" t="n"/>
-      <c r="K42" s="14" t="inlineStr"/>
+      <c r="K42" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="13" t="n"/>
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
@@ -3213,7 +3302,9 @@
         </is>
       </c>
       <c r="J43" s="9" t="n"/>
-      <c r="K43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
@@ -3264,7 +3355,9 @@
         </is>
       </c>
       <c r="J44" s="13" t="n"/>
-      <c r="K44" s="14" t="inlineStr"/>
+      <c r="K44" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" s="13" t="n"/>
       <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
@@ -3315,7 +3408,9 @@
         </is>
       </c>
       <c r="J45" s="9" t="n"/>
-      <c r="K45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
@@ -3366,7 +3461,9 @@
         </is>
       </c>
       <c r="J46" s="13" t="n"/>
-      <c r="K46" s="14" t="inlineStr"/>
+      <c r="K46" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" s="13" t="n"/>
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
@@ -3417,7 +3514,9 @@
         </is>
       </c>
       <c r="J47" s="9" t="n"/>
-      <c r="K47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
@@ -3468,7 +3567,9 @@
         </is>
       </c>
       <c r="J48" s="13" t="n"/>
-      <c r="K48" s="14" t="inlineStr"/>
+      <c r="K48" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L48" s="13" t="n"/>
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
@@ -3519,7 +3620,9 @@
         </is>
       </c>
       <c r="J49" s="9" t="n"/>
-      <c r="K49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
@@ -3570,7 +3673,9 @@
         </is>
       </c>
       <c r="J50" s="13" t="n"/>
-      <c r="K50" s="14" t="inlineStr"/>
+      <c r="K50" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L50" s="13" t="n"/>
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
@@ -3621,7 +3726,9 @@
         </is>
       </c>
       <c r="J51" s="9" t="n"/>
-      <c r="K51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
@@ -3672,7 +3779,9 @@
         </is>
       </c>
       <c r="J52" s="13" t="n"/>
-      <c r="K52" s="14" t="inlineStr"/>
+      <c r="K52" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" s="13" t="n"/>
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
@@ -3723,7 +3832,9 @@
         </is>
       </c>
       <c r="J53" s="9" t="n"/>
-      <c r="K53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
@@ -3774,7 +3885,9 @@
         </is>
       </c>
       <c r="J54" s="13" t="n"/>
-      <c r="K54" s="14" t="inlineStr"/>
+      <c r="K54" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" s="13" t="n"/>
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
@@ -3825,7 +3938,9 @@
         </is>
       </c>
       <c r="J55" s="9" t="n"/>
-      <c r="K55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
@@ -3876,7 +3991,9 @@
         </is>
       </c>
       <c r="J56" s="13" t="n"/>
-      <c r="K56" s="14" t="inlineStr"/>
+      <c r="K56" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L56" s="13" t="n"/>
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
@@ -3927,7 +4044,9 @@
         </is>
       </c>
       <c r="J57" s="9" t="n"/>
-      <c r="K57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
@@ -3978,7 +4097,9 @@
         </is>
       </c>
       <c r="J58" s="13" t="n"/>
-      <c r="K58" s="14" t="inlineStr"/>
+      <c r="K58" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" s="13" t="n"/>
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="13" t="n"/>
@@ -4029,7 +4150,9 @@
         </is>
       </c>
       <c r="J59" s="9" t="n"/>
-      <c r="K59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" s="9" t="n"/>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
@@ -4080,7 +4203,9 @@
         </is>
       </c>
       <c r="J60" s="13" t="n"/>
-      <c r="K60" s="14" t="inlineStr"/>
+      <c r="K60" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" s="13" t="n"/>
       <c r="M60" s="13" t="n"/>
       <c r="N60" s="13" t="n"/>
@@ -4131,7 +4256,9 @@
         </is>
       </c>
       <c r="J61" s="9" t="n"/>
-      <c r="K61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L61" s="9" t="n"/>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n"/>
@@ -4182,7 +4309,9 @@
         </is>
       </c>
       <c r="J62" s="13" t="n"/>
-      <c r="K62" s="14" t="inlineStr"/>
+      <c r="K62" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" s="13" t="n"/>
       <c r="M62" s="13" t="n"/>
       <c r="N62" s="13" t="n"/>
@@ -4233,7 +4362,9 @@
         </is>
       </c>
       <c r="J63" s="9" t="n"/>
-      <c r="K63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L63" s="9" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n"/>
@@ -4284,7 +4415,9 @@
         </is>
       </c>
       <c r="J64" s="13" t="n"/>
-      <c r="K64" s="14" t="inlineStr"/>
+      <c r="K64" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L64" s="13" t="n"/>
       <c r="M64" s="13" t="n"/>
       <c r="N64" s="13" t="n"/>
@@ -4335,7 +4468,9 @@
         </is>
       </c>
       <c r="J65" s="9" t="n"/>
-      <c r="K65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L65" s="9" t="n"/>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n"/>
@@ -4386,7 +4521,9 @@
         </is>
       </c>
       <c r="J66" s="13" t="n"/>
-      <c r="K66" s="14" t="inlineStr"/>
+      <c r="K66" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L66" s="13" t="n"/>
       <c r="M66" s="13" t="n"/>
       <c r="N66" s="13" t="n"/>
@@ -4437,7 +4574,9 @@
         </is>
       </c>
       <c r="J67" s="9" t="n"/>
-      <c r="K67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L67" s="9" t="n"/>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n"/>
@@ -4488,7 +4627,9 @@
         </is>
       </c>
       <c r="J68" s="13" t="n"/>
-      <c r="K68" s="14" t="inlineStr"/>
+      <c r="K68" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L68" s="13" t="n"/>
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="13" t="n"/>
@@ -4539,7 +4680,9 @@
         </is>
       </c>
       <c r="J69" s="9" t="n"/>
-      <c r="K69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" s="9" t="n"/>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n"/>
@@ -4590,7 +4733,9 @@
         </is>
       </c>
       <c r="J70" s="13" t="n"/>
-      <c r="K70" s="14" t="inlineStr"/>
+      <c r="K70" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L70" s="13" t="n"/>
       <c r="M70" s="13" t="n"/>
       <c r="N70" s="13" t="n"/>
@@ -4641,7 +4786,9 @@
         </is>
       </c>
       <c r="J71" s="9" t="n"/>
-      <c r="K71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L71" s="9" t="n"/>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n"/>
@@ -4692,7 +4839,9 @@
         </is>
       </c>
       <c r="J72" s="13" t="n"/>
-      <c r="K72" s="14" t="inlineStr"/>
+      <c r="K72" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L72" s="13" t="n"/>
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="13" t="n"/>
@@ -4743,7 +4892,9 @@
         </is>
       </c>
       <c r="J73" s="9" t="n"/>
-      <c r="K73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n"/>
@@ -4794,7 +4945,9 @@
         </is>
       </c>
       <c r="J74" s="13" t="n"/>
-      <c r="K74" s="14" t="inlineStr"/>
+      <c r="K74" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L74" s="13" t="n"/>
       <c r="M74" s="13" t="n"/>
       <c r="N74" s="13" t="n"/>
@@ -4845,7 +4998,9 @@
         </is>
       </c>
       <c r="J75" s="9" t="n"/>
-      <c r="K75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n"/>
@@ -4896,7 +5051,9 @@
         </is>
       </c>
       <c r="J76" s="13" t="n"/>
-      <c r="K76" s="14" t="inlineStr"/>
+      <c r="K76" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L76" s="13" t="n"/>
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="13" t="n"/>
@@ -4947,7 +5104,9 @@
         </is>
       </c>
       <c r="J77" s="9" t="n"/>
-      <c r="K77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
@@ -4998,7 +5157,9 @@
         </is>
       </c>
       <c r="J78" s="13" t="n"/>
-      <c r="K78" s="14" t="inlineStr"/>
+      <c r="K78" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L78" s="13" t="n"/>
       <c r="M78" s="13" t="n"/>
       <c r="N78" s="13" t="n"/>
@@ -5049,7 +5210,9 @@
         </is>
       </c>
       <c r="J79" s="9" t="n"/>
-      <c r="K79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
@@ -5100,7 +5263,9 @@
         </is>
       </c>
       <c r="J80" s="13" t="n"/>
-      <c r="K80" s="14" t="inlineStr"/>
+      <c r="K80" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L80" s="13" t="n"/>
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="13" t="n"/>
@@ -5151,7 +5316,9 @@
         </is>
       </c>
       <c r="J81" s="9" t="n"/>
-      <c r="K81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L81" s="9" t="n"/>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
@@ -5202,7 +5369,9 @@
         </is>
       </c>
       <c r="J82" s="13" t="n"/>
-      <c r="K82" s="14" t="inlineStr"/>
+      <c r="K82" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L82" s="13" t="n"/>
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="13" t="n"/>
@@ -5253,7 +5422,9 @@
         </is>
       </c>
       <c r="J83" s="9" t="n"/>
-      <c r="K83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L83" s="9" t="n"/>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
@@ -5304,7 +5475,9 @@
         </is>
       </c>
       <c r="J84" s="13" t="n"/>
-      <c r="K84" s="14" t="inlineStr"/>
+      <c r="K84" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L84" s="13" t="n"/>
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="13" t="n"/>
@@ -5355,7 +5528,9 @@
         </is>
       </c>
       <c r="J85" s="9" t="n"/>
-      <c r="K85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L85" s="9" t="n"/>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
@@ -5406,7 +5581,9 @@
         </is>
       </c>
       <c r="J86" s="13" t="n"/>
-      <c r="K86" s="14" t="inlineStr"/>
+      <c r="K86" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L86" s="13" t="n"/>
       <c r="M86" s="13" t="n"/>
       <c r="N86" s="13" t="n"/>
@@ -5457,7 +5634,9 @@
         </is>
       </c>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L87" s="9" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
@@ -5508,7 +5687,9 @@
         </is>
       </c>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="14" t="inlineStr"/>
+      <c r="K88" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L88" s="13" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="13" t="n"/>
@@ -5559,7 +5740,9 @@
         </is>
       </c>
       <c r="J89" s="9" t="n"/>
-      <c r="K89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L89" s="9" t="n"/>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
@@ -5610,7 +5793,9 @@
         </is>
       </c>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="14" t="inlineStr"/>
+      <c r="K90" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L90" s="13" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="13" t="n"/>
@@ -5661,7 +5846,9 @@
         </is>
       </c>
       <c r="J91" s="9" t="n"/>
-      <c r="K91" s="10" t="inlineStr"/>
+      <c r="K91" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" s="9" t="n"/>
       <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
@@ -5712,7 +5899,9 @@
         </is>
       </c>
       <c r="J92" s="13" t="n"/>
-      <c r="K92" s="14" t="inlineStr"/>
+      <c r="K92" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L92" s="13" t="n"/>
       <c r="M92" s="13" t="n"/>
       <c r="N92" s="13" t="n"/>
@@ -5763,7 +5952,9 @@
         </is>
       </c>
       <c r="J93" s="9" t="n"/>
-      <c r="K93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L93" s="9" t="n"/>
       <c r="M93" s="9" t="n"/>
       <c r="N93" s="9" t="n"/>
@@ -5814,7 +6005,9 @@
         </is>
       </c>
       <c r="J94" s="13" t="n"/>
-      <c r="K94" s="14" t="inlineStr"/>
+      <c r="K94" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L94" s="13" t="n"/>
       <c r="M94" s="13" t="n"/>
       <c r="N94" s="13" t="n"/>
@@ -5865,7 +6058,9 @@
         </is>
       </c>
       <c r="J95" s="9" t="n"/>
-      <c r="K95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L95" s="9" t="n"/>
       <c r="M95" s="9" t="n"/>
       <c r="N95" s="9" t="n"/>
@@ -5916,7 +6111,9 @@
         </is>
       </c>
       <c r="J96" s="13" t="n"/>
-      <c r="K96" s="14" t="inlineStr"/>
+      <c r="K96" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L96" s="13" t="n"/>
       <c r="M96" s="13" t="n"/>
       <c r="N96" s="13" t="n"/>
@@ -5967,7 +6164,9 @@
         </is>
       </c>
       <c r="J97" s="9" t="n"/>
-      <c r="K97" s="10" t="inlineStr"/>
+      <c r="K97" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L97" s="9" t="n"/>
       <c r="M97" s="9" t="n"/>
       <c r="N97" s="9" t="n"/>
@@ -6018,7 +6217,9 @@
         </is>
       </c>
       <c r="J98" s="13" t="n"/>
-      <c r="K98" s="14" t="inlineStr"/>
+      <c r="K98" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L98" s="13" t="n"/>
       <c r="M98" s="13" t="n"/>
       <c r="N98" s="13" t="n"/>
@@ -6069,7 +6270,9 @@
         </is>
       </c>
       <c r="J99" s="9" t="n"/>
-      <c r="K99" s="10" t="inlineStr"/>
+      <c r="K99" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L99" s="9" t="n"/>
       <c r="M99" s="9" t="n"/>
       <c r="N99" s="9" t="n"/>
@@ -6120,7 +6323,9 @@
         </is>
       </c>
       <c r="J100" s="13" t="n"/>
-      <c r="K100" s="14" t="inlineStr"/>
+      <c r="K100" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L100" s="13" t="n"/>
       <c r="M100" s="13" t="n"/>
       <c r="N100" s="13" t="n"/>
@@ -6171,7 +6376,9 @@
         </is>
       </c>
       <c r="J101" s="9" t="n"/>
-      <c r="K101" s="10" t="inlineStr"/>
+      <c r="K101" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L101" s="9" t="n"/>
       <c r="M101" s="9" t="n"/>
       <c r="N101" s="9" t="n"/>
@@ -6222,7 +6429,9 @@
         </is>
       </c>
       <c r="J102" s="13" t="n"/>
-      <c r="K102" s="14" t="inlineStr"/>
+      <c r="K102" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L102" s="13" t="n"/>
       <c r="M102" s="13" t="n"/>
       <c r="N102" s="13" t="n"/>
@@ -6273,7 +6482,9 @@
         </is>
       </c>
       <c r="J103" s="9" t="n"/>
-      <c r="K103" s="10" t="inlineStr"/>
+      <c r="K103" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L103" s="9" t="n"/>
       <c r="M103" s="9" t="n"/>
       <c r="N103" s="9" t="n"/>
@@ -6324,7 +6535,9 @@
         </is>
       </c>
       <c r="J104" s="13" t="n"/>
-      <c r="K104" s="14" t="inlineStr"/>
+      <c r="K104" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L104" s="13" t="n"/>
       <c r="M104" s="13" t="n"/>
       <c r="N104" s="13" t="n"/>
@@ -6375,7 +6588,9 @@
         </is>
       </c>
       <c r="J105" s="9" t="n"/>
-      <c r="K105" s="10" t="inlineStr"/>
+      <c r="K105" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" s="9" t="n"/>
       <c r="M105" s="9" t="n"/>
       <c r="N105" s="9" t="n"/>
@@ -6426,7 +6641,9 @@
         </is>
       </c>
       <c r="J106" s="13" t="n"/>
-      <c r="K106" s="14" t="inlineStr"/>
+      <c r="K106" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L106" s="13" t="n"/>
       <c r="M106" s="13" t="n"/>
       <c r="N106" s="13" t="n"/>
@@ -6477,7 +6694,9 @@
         </is>
       </c>
       <c r="J107" s="9" t="n"/>
-      <c r="K107" s="10" t="inlineStr"/>
+      <c r="K107" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L107" s="9" t="n"/>
       <c r="M107" s="9" t="n"/>
       <c r="N107" s="9" t="n"/>
@@ -6528,7 +6747,9 @@
         </is>
       </c>
       <c r="J108" s="13" t="n"/>
-      <c r="K108" s="14" t="inlineStr"/>
+      <c r="K108" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L108" s="13" t="n"/>
       <c r="M108" s="13" t="n"/>
       <c r="N108" s="13" t="n"/>
@@ -6575,7 +6796,9 @@
       </c>
       <c r="I109" s="8" t="inlineStr"/>
       <c r="J109" s="9" t="n"/>
-      <c r="K109" s="8" t="inlineStr"/>
+      <c r="K109" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L109" s="9" t="n"/>
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
@@ -6614,7 +6837,9 @@
       <c r="H110" s="12" t="inlineStr"/>
       <c r="I110" s="12" t="inlineStr"/>
       <c r="J110" s="13" t="n"/>
-      <c r="K110" s="12" t="inlineStr"/>
+      <c r="K110" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -424,6 +424,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -554,15 +572,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -576,46 +609,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -626,11 +699,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -645,31 +726,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -678,11 +783,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주 발주일 (양산 외주발주)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 외주 발주일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 외부업체에 양산 가공품을 ★실제 발주한 날짜★ 기입
@@ -690,38 +803,63 @@
 • 외주입고일과 짝 — 발주 후 입고까지 추적
 • 비워두면: 외주 미발주 상태
 • 구매팀 전용 컬럼 (양산 외주 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 외주 입고일 (양산 외주발주)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 외부업체에서 양산 가공품이 실제 입고된 날짜
 • 비워두면: 대시보드 외주현황에 '진행중'
 • 입고일 입력 시: '입고완료' 자동 분류</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1042,7 +1180,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="88" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1063,7 +1201,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="83" t="inlineStr">
+      <c r="A2" s="89" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1081,9 +1219,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="84" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:44</t>
+      <c r="O2" s="90" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -130,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -210,11 +210,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -488,6 +517,17 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1180,7 +1220,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="88" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1201,7 +1241,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="92" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1216,14 +1256,14 @@
       <c r="I2" s="16" t="n"/>
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
-      <c r="L2" s="16" t="n"/>
-      <c r="M2" s="16" t="n"/>
-      <c r="N2" s="17" t="n"/>
-      <c r="O2" s="90" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="93" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:58</t>
+        </is>
+      </c>
+      <c r="N2" s="94" t="n"/>
+      <c r="O2" s="95" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -7495,9 +7535,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1210,8 +1219,8 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" style="43" min="12" max="12"/>
-    <col width="12" customWidth="1" style="43" min="13" max="13"/>
+    <col width="5" customWidth="1" style="43" min="12" max="12"/>
+    <col width="5" customWidth="1" style="43" min="13" max="13"/>
     <col width="10" customWidth="1" style="43" min="14" max="14"/>
     <col width="28" customWidth="1" style="43" min="15" max="15"/>
     <col width="12" customWidth="1" style="43" min="16" max="16"/>
@@ -1220,7 +1229,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="91" t="inlineStr">
+      <c r="A1" s="96" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1241,7 +1250,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="92" t="inlineStr">
+      <c r="A2" s="97" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1257,13 +1266,13 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="93" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:58</t>
-        </is>
-      </c>
-      <c r="N2" s="94" t="n"/>
-      <c r="O2" s="95" t="n"/>
+      <c r="M2" s="98" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="N2" s="16" t="n"/>
+      <c r="O2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1219,8 +1228,8 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" style="43" min="12" max="12"/>
-    <col width="5" customWidth="1" style="43" min="13" max="13"/>
+    <col width="7" customWidth="1" style="43" min="12" max="12"/>
+    <col width="7" customWidth="1" style="43" min="13" max="13"/>
     <col width="10" customWidth="1" style="43" min="14" max="14"/>
     <col width="28" customWidth="1" style="43" min="15" max="15"/>
     <col width="12" customWidth="1" style="43" min="16" max="16"/>
@@ -1229,7 +1238,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="96" t="inlineStr">
+      <c r="A1" s="99" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1250,7 +1259,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="97" t="inlineStr">
+      <c r="A2" s="100" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1266,9 +1275,9 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="98" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="M2" s="101" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="N2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -873,6 +882,27 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
+          <t>▣ 외주 입고예정일 (외주 발주 후 예정)
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-07-15
+• 외주(자재·양산 가공품) 발주 시
+  외부업체와 약속한 ★입고 완료 예정일★ 기입
+📋 운영:
+  ▸ 발주 시 예정일 입력
+  ▸ 실제 입고일과 비교 → 지연 여부 추적
+  ▸ 비워두면: 미발주 또는 일정 미정</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
           <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
@@ -882,7 +912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -901,7 +931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1214,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O140"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1230,15 +1260,15 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" style="43" min="12" max="12"/>
     <col width="7" customWidth="1" style="43" min="13" max="13"/>
-    <col width="10" customWidth="1" style="43" min="14" max="14"/>
-    <col width="28" customWidth="1" style="43" min="15" max="15"/>
-    <col width="12" customWidth="1" style="43" min="16" max="16"/>
+    <col width="7" customWidth="1" style="43" min="14" max="14"/>
+    <col width="10" customWidth="1" style="43" min="15" max="15"/>
+    <col width="28" customWidth="1" style="43" min="16" max="16"/>
     <col width="10" customWidth="1" style="43" min="17" max="17"/>
     <col width="28" customWidth="1" style="43" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1256,10 +1286,11 @@
       <c r="L1" s="16" t="n"/>
       <c r="M1" s="16" t="n"/>
       <c r="N1" s="16" t="n"/>
-      <c r="O1" s="17" t="n"/>
+      <c r="O1" s="16" t="n"/>
+      <c r="P1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="100" t="inlineStr">
+      <c r="A2" s="103" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1274,14 +1305,13 @@
       <c r="I2" s="16" t="n"/>
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
-      <c r="L2" s="17" t="n"/>
-      <c r="M2" s="101" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
-        </is>
-      </c>
-      <c r="N2" s="16" t="n"/>
-      <c r="O2" s="17" t="n"/>
+      <c r="L2" s="16" t="n"/>
+      <c r="M2" s="17" t="n"/>
+      <c r="N2" s="104" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1349,12 +1379,17 @@
           <t>PO후입력</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1425,15 +1460,21 @@
       <c r="M4" s="61" t="inlineStr">
         <is>
           <t>외주
+예정일</t>
+        </is>
+      </c>
+      <c r="N4" s="61" t="inlineStr">
+        <is>
+          <t>외주
 입고일</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1490,7 +1531,8 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
-      <c r="O5" s="22" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1543,7 +1585,8 @@
       <c r="L6" s="13" t="n"/>
       <c r="M6" s="13" t="n"/>
       <c r="N6" s="13" t="n"/>
-      <c r="O6" s="24" t="n"/>
+      <c r="O6" s="13" t="n"/>
+      <c r="P6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1596,7 +1639,8 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
-      <c r="O7" s="22" t="n"/>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1649,7 +1693,8 @@
       <c r="L8" s="13" t="n"/>
       <c r="M8" s="13" t="n"/>
       <c r="N8" s="13" t="n"/>
-      <c r="O8" s="24" t="n"/>
+      <c r="O8" s="13" t="n"/>
+      <c r="P8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1702,7 +1747,8 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
-      <c r="O9" s="22" t="n"/>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1755,7 +1801,8 @@
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
-      <c r="O10" s="24" t="n"/>
+      <c r="O10" s="13" t="n"/>
+      <c r="P10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1808,7 +1855,8 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
-      <c r="O11" s="22" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1861,7 +1909,8 @@
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
       <c r="N12" s="13" t="n"/>
-      <c r="O12" s="24" t="n"/>
+      <c r="O12" s="13" t="n"/>
+      <c r="P12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1914,7 +1963,8 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
-      <c r="O13" s="22" t="n"/>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1967,7 +2017,8 @@
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
-      <c r="O14" s="24" t="n"/>
+      <c r="O14" s="13" t="n"/>
+      <c r="P14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2020,7 +2071,8 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
-      <c r="O15" s="22" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -2073,7 +2125,8 @@
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
-      <c r="O16" s="24" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2126,7 +2179,8 @@
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
-      <c r="O17" s="22" t="n"/>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -2179,7 +2233,8 @@
       <c r="L18" s="13" t="n"/>
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
-      <c r="O18" s="24" t="n"/>
+      <c r="O18" s="13" t="n"/>
+      <c r="P18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2232,7 +2287,8 @@
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
-      <c r="O19" s="22" t="n"/>
+      <c r="O19" s="9" t="n"/>
+      <c r="P19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2285,7 +2341,8 @@
       <c r="L20" s="13" t="n"/>
       <c r="M20" s="13" t="n"/>
       <c r="N20" s="13" t="n"/>
-      <c r="O20" s="24" t="n"/>
+      <c r="O20" s="13" t="n"/>
+      <c r="P20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2338,7 +2395,8 @@
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
-      <c r="O21" s="22" t="n"/>
+      <c r="O21" s="9" t="n"/>
+      <c r="P21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2391,7 +2449,8 @@
       <c r="L22" s="13" t="n"/>
       <c r="M22" s="13" t="n"/>
       <c r="N22" s="13" t="n"/>
-      <c r="O22" s="24" t="n"/>
+      <c r="O22" s="13" t="n"/>
+      <c r="P22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2444,7 +2503,8 @@
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
-      <c r="O23" s="22" t="n"/>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2497,7 +2557,8 @@
       <c r="L24" s="13" t="n"/>
       <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
-      <c r="O24" s="24" t="n"/>
+      <c r="O24" s="13" t="n"/>
+      <c r="P24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2550,7 +2611,8 @@
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
-      <c r="O25" s="22" t="n"/>
+      <c r="O25" s="9" t="n"/>
+      <c r="P25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2603,7 +2665,8 @@
       <c r="L26" s="13" t="n"/>
       <c r="M26" s="13" t="n"/>
       <c r="N26" s="13" t="n"/>
-      <c r="O26" s="24" t="n"/>
+      <c r="O26" s="13" t="n"/>
+      <c r="P26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2656,7 +2719,8 @@
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
-      <c r="O27" s="22" t="n"/>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n">
@@ -2709,7 +2773,8 @@
       <c r="L28" s="13" t="n"/>
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
-      <c r="O28" s="24" t="n"/>
+      <c r="O28" s="13" t="n"/>
+      <c r="P28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -2762,7 +2827,8 @@
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
-      <c r="O29" s="22" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n">
@@ -2815,7 +2881,8 @@
       <c r="L30" s="13" t="n"/>
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
-      <c r="O30" s="24" t="n"/>
+      <c r="O30" s="13" t="n"/>
+      <c r="P30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -2868,7 +2935,8 @@
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
-      <c r="O31" s="22" t="n"/>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n">
@@ -2921,7 +2989,8 @@
       <c r="L32" s="13" t="n"/>
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
-      <c r="O32" s="24" t="n"/>
+      <c r="O32" s="13" t="n"/>
+      <c r="P32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -2974,7 +3043,8 @@
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
-      <c r="O33" s="22" t="n"/>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n">
@@ -3027,7 +3097,8 @@
       <c r="L34" s="13" t="n"/>
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
-      <c r="O34" s="24" t="n"/>
+      <c r="O34" s="13" t="n"/>
+      <c r="P34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -3080,7 +3151,8 @@
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
-      <c r="O35" s="22" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n">
@@ -3133,7 +3205,8 @@
       <c r="L36" s="13" t="n"/>
       <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
-      <c r="O36" s="24" t="n"/>
+      <c r="O36" s="13" t="n"/>
+      <c r="P36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -3186,7 +3259,8 @@
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
-      <c r="O37" s="22" t="n"/>
+      <c r="O37" s="9" t="n"/>
+      <c r="P37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n">
@@ -3239,7 +3313,8 @@
       <c r="L38" s="13" t="n"/>
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
-      <c r="O38" s="24" t="n"/>
+      <c r="O38" s="13" t="n"/>
+      <c r="P38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -3292,7 +3367,8 @@
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
-      <c r="O39" s="22" t="n"/>
+      <c r="O39" s="9" t="n"/>
+      <c r="P39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n">
@@ -3345,7 +3421,8 @@
       <c r="L40" s="13" t="n"/>
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
-      <c r="O40" s="24" t="n"/>
+      <c r="O40" s="13" t="n"/>
+      <c r="P40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -3398,7 +3475,8 @@
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
-      <c r="O41" s="22" t="n"/>
+      <c r="O41" s="9" t="n"/>
+      <c r="P41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n">
@@ -3451,7 +3529,8 @@
       <c r="L42" s="13" t="n"/>
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
-      <c r="O42" s="24" t="n"/>
+      <c r="O42" s="13" t="n"/>
+      <c r="P42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -3504,7 +3583,8 @@
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
-      <c r="O43" s="22" t="n"/>
+      <c r="O43" s="9" t="n"/>
+      <c r="P43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n">
@@ -3557,7 +3637,8 @@
       <c r="L44" s="13" t="n"/>
       <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
-      <c r="O44" s="24" t="n"/>
+      <c r="O44" s="13" t="n"/>
+      <c r="P44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -3610,7 +3691,8 @@
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
-      <c r="O45" s="22" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n">
@@ -3663,7 +3745,8 @@
       <c r="L46" s="13" t="n"/>
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
-      <c r="O46" s="24" t="n"/>
+      <c r="O46" s="13" t="n"/>
+      <c r="P46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -3716,7 +3799,8 @@
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
-      <c r="O47" s="22" t="n"/>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n">
@@ -3769,7 +3853,8 @@
       <c r="L48" s="13" t="n"/>
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
-      <c r="O48" s="24" t="n"/>
+      <c r="O48" s="13" t="n"/>
+      <c r="P48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -3822,7 +3907,8 @@
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
-      <c r="O49" s="22" t="n"/>
+      <c r="O49" s="9" t="n"/>
+      <c r="P49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n">
@@ -3875,7 +3961,8 @@
       <c r="L50" s="13" t="n"/>
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
-      <c r="O50" s="24" t="n"/>
+      <c r="O50" s="13" t="n"/>
+      <c r="P50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -3928,7 +4015,8 @@
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
-      <c r="O51" s="22" t="n"/>
+      <c r="O51" s="9" t="n"/>
+      <c r="P51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -3981,7 +4069,8 @@
       <c r="L52" s="13" t="n"/>
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
-      <c r="O52" s="24" t="n"/>
+      <c r="O52" s="13" t="n"/>
+      <c r="P52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -4034,7 +4123,8 @@
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
-      <c r="O53" s="22" t="n"/>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n">
@@ -4087,7 +4177,8 @@
       <c r="L54" s="13" t="n"/>
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
-      <c r="O54" s="24" t="n"/>
+      <c r="O54" s="13" t="n"/>
+      <c r="P54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -4140,7 +4231,8 @@
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
-      <c r="O55" s="22" t="n"/>
+      <c r="O55" s="9" t="n"/>
+      <c r="P55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n">
@@ -4193,7 +4285,8 @@
       <c r="L56" s="13" t="n"/>
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
-      <c r="O56" s="24" t="n"/>
+      <c r="O56" s="13" t="n"/>
+      <c r="P56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -4246,7 +4339,8 @@
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
-      <c r="O57" s="22" t="n"/>
+      <c r="O57" s="9" t="n"/>
+      <c r="P57" s="22" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -4299,7 +4393,8 @@
       <c r="L58" s="13" t="n"/>
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="13" t="n"/>
-      <c r="O58" s="24" t="n"/>
+      <c r="O58" s="13" t="n"/>
+      <c r="P58" s="24" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -4352,7 +4447,8 @@
       <c r="L59" s="9" t="n"/>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
-      <c r="O59" s="22" t="n"/>
+      <c r="O59" s="9" t="n"/>
+      <c r="P59" s="22" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="12" t="n">
@@ -4405,7 +4501,8 @@
       <c r="L60" s="13" t="n"/>
       <c r="M60" s="13" t="n"/>
       <c r="N60" s="13" t="n"/>
-      <c r="O60" s="24" t="n"/>
+      <c r="O60" s="13" t="n"/>
+      <c r="P60" s="24" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -4458,7 +4555,8 @@
       <c r="L61" s="9" t="n"/>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n"/>
-      <c r="O61" s="22" t="n"/>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="22" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="12" t="n">
@@ -4511,7 +4609,8 @@
       <c r="L62" s="13" t="n"/>
       <c r="M62" s="13" t="n"/>
       <c r="N62" s="13" t="n"/>
-      <c r="O62" s="24" t="n"/>
+      <c r="O62" s="13" t="n"/>
+      <c r="P62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -4564,7 +4663,8 @@
       <c r="L63" s="9" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n"/>
-      <c r="O63" s="22" t="n"/>
+      <c r="O63" s="9" t="n"/>
+      <c r="P63" s="22" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="12" t="n">
@@ -4617,7 +4717,8 @@
       <c r="L64" s="13" t="n"/>
       <c r="M64" s="13" t="n"/>
       <c r="N64" s="13" t="n"/>
-      <c r="O64" s="24" t="n"/>
+      <c r="O64" s="13" t="n"/>
+      <c r="P64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="8" t="n">
@@ -4670,7 +4771,8 @@
       <c r="L65" s="9" t="n"/>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n"/>
-      <c r="O65" s="22" t="n"/>
+      <c r="O65" s="9" t="n"/>
+      <c r="P65" s="22" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="12" t="n">
@@ -4723,7 +4825,8 @@
       <c r="L66" s="13" t="n"/>
       <c r="M66" s="13" t="n"/>
       <c r="N66" s="13" t="n"/>
-      <c r="O66" s="24" t="n"/>
+      <c r="O66" s="13" t="n"/>
+      <c r="P66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="8" t="n">
@@ -4776,7 +4879,8 @@
       <c r="L67" s="9" t="n"/>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n"/>
-      <c r="O67" s="22" t="n"/>
+      <c r="O67" s="9" t="n"/>
+      <c r="P67" s="22" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="12" t="n">
@@ -4829,7 +4933,8 @@
       <c r="L68" s="13" t="n"/>
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="13" t="n"/>
-      <c r="O68" s="24" t="n"/>
+      <c r="O68" s="13" t="n"/>
+      <c r="P68" s="24" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="8" t="n">
@@ -4882,7 +4987,8 @@
       <c r="L69" s="9" t="n"/>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n"/>
-      <c r="O69" s="22" t="n"/>
+      <c r="O69" s="9" t="n"/>
+      <c r="P69" s="22" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="12" t="n">
@@ -4935,7 +5041,8 @@
       <c r="L70" s="13" t="n"/>
       <c r="M70" s="13" t="n"/>
       <c r="N70" s="13" t="n"/>
-      <c r="O70" s="24" t="n"/>
+      <c r="O70" s="13" t="n"/>
+      <c r="P70" s="24" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="8" t="n">
@@ -4988,7 +5095,8 @@
       <c r="L71" s="9" t="n"/>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n"/>
-      <c r="O71" s="22" t="n"/>
+      <c r="O71" s="9" t="n"/>
+      <c r="P71" s="22" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="12" t="n">
@@ -5041,7 +5149,8 @@
       <c r="L72" s="13" t="n"/>
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="13" t="n"/>
-      <c r="O72" s="24" t="n"/>
+      <c r="O72" s="13" t="n"/>
+      <c r="P72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="8" t="n">
@@ -5094,7 +5203,8 @@
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n"/>
-      <c r="O73" s="22" t="n"/>
+      <c r="O73" s="9" t="n"/>
+      <c r="P73" s="22" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="12" t="n">
@@ -5147,7 +5257,8 @@
       <c r="L74" s="13" t="n"/>
       <c r="M74" s="13" t="n"/>
       <c r="N74" s="13" t="n"/>
-      <c r="O74" s="24" t="n"/>
+      <c r="O74" s="13" t="n"/>
+      <c r="P74" s="24" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="n">
@@ -5200,7 +5311,8 @@
       <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n"/>
-      <c r="O75" s="22" t="n"/>
+      <c r="O75" s="9" t="n"/>
+      <c r="P75" s="22" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="12" t="n">
@@ -5253,7 +5365,8 @@
       <c r="L76" s="13" t="n"/>
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="13" t="n"/>
-      <c r="O76" s="24" t="n"/>
+      <c r="O76" s="13" t="n"/>
+      <c r="P76" s="24" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="8" t="n">
@@ -5306,7 +5419,8 @@
       <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
-      <c r="O77" s="22" t="n"/>
+      <c r="O77" s="9" t="n"/>
+      <c r="P77" s="22" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="12" t="n">
@@ -5359,7 +5473,8 @@
       <c r="L78" s="13" t="n"/>
       <c r="M78" s="13" t="n"/>
       <c r="N78" s="13" t="n"/>
-      <c r="O78" s="24" t="n"/>
+      <c r="O78" s="13" t="n"/>
+      <c r="P78" s="24" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="8" t="n">
@@ -5412,7 +5527,8 @@
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
-      <c r="O79" s="22" t="n"/>
+      <c r="O79" s="9" t="n"/>
+      <c r="P79" s="22" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="12" t="n">
@@ -5465,7 +5581,8 @@
       <c r="L80" s="13" t="n"/>
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="13" t="n"/>
-      <c r="O80" s="24" t="n"/>
+      <c r="O80" s="13" t="n"/>
+      <c r="P80" s="24" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="8" t="n">
@@ -5518,7 +5635,8 @@
       <c r="L81" s="9" t="n"/>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
-      <c r="O81" s="22" t="n"/>
+      <c r="O81" s="9" t="n"/>
+      <c r="P81" s="22" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="12" t="n">
@@ -5571,7 +5689,8 @@
       <c r="L82" s="13" t="n"/>
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="13" t="n"/>
-      <c r="O82" s="24" t="n"/>
+      <c r="O82" s="13" t="n"/>
+      <c r="P82" s="24" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="8" t="n">
@@ -5624,7 +5743,8 @@
       <c r="L83" s="9" t="n"/>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
-      <c r="O83" s="22" t="n"/>
+      <c r="O83" s="9" t="n"/>
+      <c r="P83" s="22" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -5677,7 +5797,8 @@
       <c r="L84" s="13" t="n"/>
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="13" t="n"/>
-      <c r="O84" s="24" t="n"/>
+      <c r="O84" s="13" t="n"/>
+      <c r="P84" s="24" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="8" t="n">
@@ -5730,7 +5851,8 @@
       <c r="L85" s="9" t="n"/>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
-      <c r="O85" s="22" t="n"/>
+      <c r="O85" s="9" t="n"/>
+      <c r="P85" s="22" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="12" t="n">
@@ -5783,7 +5905,8 @@
       <c r="L86" s="13" t="n"/>
       <c r="M86" s="13" t="n"/>
       <c r="N86" s="13" t="n"/>
-      <c r="O86" s="24" t="n"/>
+      <c r="O86" s="13" t="n"/>
+      <c r="P86" s="24" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -5836,7 +5959,8 @@
       <c r="L87" s="9" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
-      <c r="O87" s="22" t="n"/>
+      <c r="O87" s="9" t="n"/>
+      <c r="P87" s="22" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="12" t="n">
@@ -5889,7 +6013,8 @@
       <c r="L88" s="13" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="13" t="n"/>
-      <c r="O88" s="24" t="n"/>
+      <c r="O88" s="13" t="n"/>
+      <c r="P88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="8" t="n">
@@ -5942,7 +6067,8 @@
       <c r="L89" s="9" t="n"/>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
-      <c r="O89" s="22" t="n"/>
+      <c r="O89" s="9" t="n"/>
+      <c r="P89" s="22" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="12" t="n">
@@ -5995,7 +6121,8 @@
       <c r="L90" s="13" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="13" t="n"/>
-      <c r="O90" s="24" t="n"/>
+      <c r="O90" s="13" t="n"/>
+      <c r="P90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="8" t="n">
@@ -6048,7 +6175,8 @@
       <c r="L91" s="9" t="n"/>
       <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
-      <c r="O91" s="22" t="n"/>
+      <c r="O91" s="9" t="n"/>
+      <c r="P91" s="22" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="12" t="n">
@@ -6101,7 +6229,8 @@
       <c r="L92" s="13" t="n"/>
       <c r="M92" s="13" t="n"/>
       <c r="N92" s="13" t="n"/>
-      <c r="O92" s="24" t="n"/>
+      <c r="O92" s="13" t="n"/>
+      <c r="P92" s="24" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="8" t="n">
@@ -6154,7 +6283,8 @@
       <c r="L93" s="9" t="n"/>
       <c r="M93" s="9" t="n"/>
       <c r="N93" s="9" t="n"/>
-      <c r="O93" s="22" t="n"/>
+      <c r="O93" s="9" t="n"/>
+      <c r="P93" s="22" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="12" t="n">
@@ -6207,7 +6337,8 @@
       <c r="L94" s="13" t="n"/>
       <c r="M94" s="13" t="n"/>
       <c r="N94" s="13" t="n"/>
-      <c r="O94" s="24" t="n"/>
+      <c r="O94" s="13" t="n"/>
+      <c r="P94" s="24" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="8" t="n">
@@ -6260,7 +6391,8 @@
       <c r="L95" s="9" t="n"/>
       <c r="M95" s="9" t="n"/>
       <c r="N95" s="9" t="n"/>
-      <c r="O95" s="22" t="n"/>
+      <c r="O95" s="9" t="n"/>
+      <c r="P95" s="22" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="n">
@@ -6313,7 +6445,8 @@
       <c r="L96" s="13" t="n"/>
       <c r="M96" s="13" t="n"/>
       <c r="N96" s="13" t="n"/>
-      <c r="O96" s="24" t="n"/>
+      <c r="O96" s="13" t="n"/>
+      <c r="P96" s="24" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="8" t="n">
@@ -6366,7 +6499,8 @@
       <c r="L97" s="9" t="n"/>
       <c r="M97" s="9" t="n"/>
       <c r="N97" s="9" t="n"/>
-      <c r="O97" s="22" t="n"/>
+      <c r="O97" s="9" t="n"/>
+      <c r="P97" s="22" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="n">
@@ -6419,7 +6553,8 @@
       <c r="L98" s="13" t="n"/>
       <c r="M98" s="13" t="n"/>
       <c r="N98" s="13" t="n"/>
-      <c r="O98" s="24" t="n"/>
+      <c r="O98" s="13" t="n"/>
+      <c r="P98" s="24" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -6472,7 +6607,8 @@
       <c r="L99" s="9" t="n"/>
       <c r="M99" s="9" t="n"/>
       <c r="N99" s="9" t="n"/>
-      <c r="O99" s="22" t="n"/>
+      <c r="O99" s="9" t="n"/>
+      <c r="P99" s="22" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="n">
@@ -6525,7 +6661,8 @@
       <c r="L100" s="13" t="n"/>
       <c r="M100" s="13" t="n"/>
       <c r="N100" s="13" t="n"/>
-      <c r="O100" s="24" t="n"/>
+      <c r="O100" s="13" t="n"/>
+      <c r="P100" s="24" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="8" t="n">
@@ -6578,7 +6715,8 @@
       <c r="L101" s="9" t="n"/>
       <c r="M101" s="9" t="n"/>
       <c r="N101" s="9" t="n"/>
-      <c r="O101" s="22" t="n"/>
+      <c r="O101" s="9" t="n"/>
+      <c r="P101" s="22" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="n">
@@ -6631,7 +6769,8 @@
       <c r="L102" s="13" t="n"/>
       <c r="M102" s="13" t="n"/>
       <c r="N102" s="13" t="n"/>
-      <c r="O102" s="24" t="n"/>
+      <c r="O102" s="13" t="n"/>
+      <c r="P102" s="24" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="8" t="n">
@@ -6684,7 +6823,8 @@
       <c r="L103" s="9" t="n"/>
       <c r="M103" s="9" t="n"/>
       <c r="N103" s="9" t="n"/>
-      <c r="O103" s="22" t="n"/>
+      <c r="O103" s="9" t="n"/>
+      <c r="P103" s="22" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="n">
@@ -6737,7 +6877,8 @@
       <c r="L104" s="13" t="n"/>
       <c r="M104" s="13" t="n"/>
       <c r="N104" s="13" t="n"/>
-      <c r="O104" s="24" t="n"/>
+      <c r="O104" s="13" t="n"/>
+      <c r="P104" s="24" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="8" t="n">
@@ -6790,7 +6931,8 @@
       <c r="L105" s="9" t="n"/>
       <c r="M105" s="9" t="n"/>
       <c r="N105" s="9" t="n"/>
-      <c r="O105" s="22" t="n"/>
+      <c r="O105" s="9" t="n"/>
+      <c r="P105" s="22" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="n">
@@ -6843,7 +6985,8 @@
       <c r="L106" s="13" t="n"/>
       <c r="M106" s="13" t="n"/>
       <c r="N106" s="13" t="n"/>
-      <c r="O106" s="24" t="n"/>
+      <c r="O106" s="13" t="n"/>
+      <c r="P106" s="24" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -6896,7 +7039,8 @@
       <c r="L107" s="9" t="n"/>
       <c r="M107" s="9" t="n"/>
       <c r="N107" s="9" t="n"/>
-      <c r="O107" s="22" t="n"/>
+      <c r="O107" s="9" t="n"/>
+      <c r="P107" s="22" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -6949,7 +7093,8 @@
       <c r="L108" s="13" t="n"/>
       <c r="M108" s="13" t="n"/>
       <c r="N108" s="13" t="n"/>
-      <c r="O108" s="24" t="n"/>
+      <c r="O108" s="13" t="n"/>
+      <c r="P108" s="24" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="8" t="n">
@@ -6998,7 +7143,8 @@
       <c r="L109" s="9" t="n"/>
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
-      <c r="O109" s="22" t="n"/>
+      <c r="O109" s="9" t="n"/>
+      <c r="P109" s="22" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="n">
@@ -7039,7 +7185,8 @@
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>
-      <c r="O110" s="24" t="n"/>
+      <c r="O110" s="13" t="n"/>
+      <c r="P110" s="24" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="8" t="n"/>
@@ -7056,7 +7203,8 @@
       <c r="L111" s="9" t="n"/>
       <c r="M111" s="9" t="n"/>
       <c r="N111" s="9" t="n"/>
-      <c r="O111" s="22" t="n"/>
+      <c r="O111" s="9" t="n"/>
+      <c r="P111" s="22" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="n"/>
@@ -7073,7 +7221,8 @@
       <c r="L112" s="13" t="n"/>
       <c r="M112" s="13" t="n"/>
       <c r="N112" s="13" t="n"/>
-      <c r="O112" s="24" t="n"/>
+      <c r="O112" s="13" t="n"/>
+      <c r="P112" s="24" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="8" t="n"/>
@@ -7090,7 +7239,8 @@
       <c r="L113" s="9" t="n"/>
       <c r="M113" s="9" t="n"/>
       <c r="N113" s="9" t="n"/>
-      <c r="O113" s="22" t="n"/>
+      <c r="O113" s="9" t="n"/>
+      <c r="P113" s="22" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="n"/>
@@ -7107,7 +7257,8 @@
       <c r="L114" s="13" t="n"/>
       <c r="M114" s="13" t="n"/>
       <c r="N114" s="13" t="n"/>
-      <c r="O114" s="24" t="n"/>
+      <c r="O114" s="13" t="n"/>
+      <c r="P114" s="24" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="8" t="n"/>
@@ -7124,7 +7275,8 @@
       <c r="L115" s="9" t="n"/>
       <c r="M115" s="9" t="n"/>
       <c r="N115" s="9" t="n"/>
-      <c r="O115" s="22" t="n"/>
+      <c r="O115" s="9" t="n"/>
+      <c r="P115" s="22" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="n"/>
@@ -7141,7 +7293,8 @@
       <c r="L116" s="13" t="n"/>
       <c r="M116" s="13" t="n"/>
       <c r="N116" s="13" t="n"/>
-      <c r="O116" s="24" t="n"/>
+      <c r="O116" s="13" t="n"/>
+      <c r="P116" s="24" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="8" t="n"/>
@@ -7158,7 +7311,8 @@
       <c r="L117" s="9" t="n"/>
       <c r="M117" s="9" t="n"/>
       <c r="N117" s="9" t="n"/>
-      <c r="O117" s="22" t="n"/>
+      <c r="O117" s="9" t="n"/>
+      <c r="P117" s="22" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="12" t="n"/>
@@ -7175,7 +7329,8 @@
       <c r="L118" s="13" t="n"/>
       <c r="M118" s="13" t="n"/>
       <c r="N118" s="13" t="n"/>
-      <c r="O118" s="24" t="n"/>
+      <c r="O118" s="13" t="n"/>
+      <c r="P118" s="24" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="8" t="n"/>
@@ -7192,7 +7347,8 @@
       <c r="L119" s="9" t="n"/>
       <c r="M119" s="9" t="n"/>
       <c r="N119" s="9" t="n"/>
-      <c r="O119" s="22" t="n"/>
+      <c r="O119" s="9" t="n"/>
+      <c r="P119" s="22" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="n"/>
@@ -7209,7 +7365,8 @@
       <c r="L120" s="13" t="n"/>
       <c r="M120" s="13" t="n"/>
       <c r="N120" s="13" t="n"/>
-      <c r="O120" s="24" t="n"/>
+      <c r="O120" s="13" t="n"/>
+      <c r="P120" s="24" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="8" t="n"/>
@@ -7226,7 +7383,8 @@
       <c r="L121" s="9" t="n"/>
       <c r="M121" s="9" t="n"/>
       <c r="N121" s="9" t="n"/>
-      <c r="O121" s="22" t="n"/>
+      <c r="O121" s="9" t="n"/>
+      <c r="P121" s="22" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="n"/>
@@ -7243,7 +7401,8 @@
       <c r="L122" s="13" t="n"/>
       <c r="M122" s="13" t="n"/>
       <c r="N122" s="13" t="n"/>
-      <c r="O122" s="24" t="n"/>
+      <c r="O122" s="13" t="n"/>
+      <c r="P122" s="24" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="8" t="n"/>
@@ -7260,7 +7419,8 @@
       <c r="L123" s="9" t="n"/>
       <c r="M123" s="9" t="n"/>
       <c r="N123" s="9" t="n"/>
-      <c r="O123" s="22" t="n"/>
+      <c r="O123" s="9" t="n"/>
+      <c r="P123" s="22" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="n"/>
@@ -7277,7 +7437,8 @@
       <c r="L124" s="13" t="n"/>
       <c r="M124" s="13" t="n"/>
       <c r="N124" s="13" t="n"/>
-      <c r="O124" s="24" t="n"/>
+      <c r="O124" s="13" t="n"/>
+      <c r="P124" s="24" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="8" t="n"/>
@@ -7294,7 +7455,8 @@
       <c r="L125" s="9" t="n"/>
       <c r="M125" s="9" t="n"/>
       <c r="N125" s="9" t="n"/>
-      <c r="O125" s="22" t="n"/>
+      <c r="O125" s="9" t="n"/>
+      <c r="P125" s="22" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="12" t="n"/>
@@ -7311,7 +7473,8 @@
       <c r="L126" s="13" t="n"/>
       <c r="M126" s="13" t="n"/>
       <c r="N126" s="13" t="n"/>
-      <c r="O126" s="24" t="n"/>
+      <c r="O126" s="13" t="n"/>
+      <c r="P126" s="24" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="8" t="n"/>
@@ -7328,7 +7491,8 @@
       <c r="L127" s="9" t="n"/>
       <c r="M127" s="9" t="n"/>
       <c r="N127" s="9" t="n"/>
-      <c r="O127" s="22" t="n"/>
+      <c r="O127" s="9" t="n"/>
+      <c r="P127" s="22" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="n"/>
@@ -7345,7 +7509,8 @@
       <c r="L128" s="13" t="n"/>
       <c r="M128" s="13" t="n"/>
       <c r="N128" s="13" t="n"/>
-      <c r="O128" s="24" t="n"/>
+      <c r="O128" s="13" t="n"/>
+      <c r="P128" s="24" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="8" t="n"/>
@@ -7362,7 +7527,8 @@
       <c r="L129" s="9" t="n"/>
       <c r="M129" s="9" t="n"/>
       <c r="N129" s="9" t="n"/>
-      <c r="O129" s="22" t="n"/>
+      <c r="O129" s="9" t="n"/>
+      <c r="P129" s="22" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="12" t="n"/>
@@ -7379,7 +7545,8 @@
       <c r="L130" s="13" t="n"/>
       <c r="M130" s="13" t="n"/>
       <c r="N130" s="13" t="n"/>
-      <c r="O130" s="24" t="n"/>
+      <c r="O130" s="13" t="n"/>
+      <c r="P130" s="24" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="8" t="n"/>
@@ -7396,7 +7563,8 @@
       <c r="L131" s="9" t="n"/>
       <c r="M131" s="9" t="n"/>
       <c r="N131" s="9" t="n"/>
-      <c r="O131" s="22" t="n"/>
+      <c r="O131" s="9" t="n"/>
+      <c r="P131" s="22" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="12" t="n"/>
@@ -7413,7 +7581,8 @@
       <c r="L132" s="13" t="n"/>
       <c r="M132" s="13" t="n"/>
       <c r="N132" s="13" t="n"/>
-      <c r="O132" s="24" t="n"/>
+      <c r="O132" s="13" t="n"/>
+      <c r="P132" s="24" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="8" t="n"/>
@@ -7430,7 +7599,8 @@
       <c r="L133" s="9" t="n"/>
       <c r="M133" s="9" t="n"/>
       <c r="N133" s="9" t="n"/>
-      <c r="O133" s="22" t="n"/>
+      <c r="O133" s="9" t="n"/>
+      <c r="P133" s="22" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="12" t="n"/>
@@ -7447,7 +7617,8 @@
       <c r="L134" s="13" t="n"/>
       <c r="M134" s="13" t="n"/>
       <c r="N134" s="13" t="n"/>
-      <c r="O134" s="24" t="n"/>
+      <c r="O134" s="13" t="n"/>
+      <c r="P134" s="24" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="8" t="n"/>
@@ -7464,7 +7635,8 @@
       <c r="L135" s="9" t="n"/>
       <c r="M135" s="9" t="n"/>
       <c r="N135" s="9" t="n"/>
-      <c r="O135" s="22" t="n"/>
+      <c r="O135" s="9" t="n"/>
+      <c r="P135" s="22" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="12" t="n"/>
@@ -7481,7 +7653,8 @@
       <c r="L136" s="13" t="n"/>
       <c r="M136" s="13" t="n"/>
       <c r="N136" s="13" t="n"/>
-      <c r="O136" s="24" t="n"/>
+      <c r="O136" s="13" t="n"/>
+      <c r="P136" s="24" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="8" t="n"/>
@@ -7498,7 +7671,8 @@
       <c r="L137" s="9" t="n"/>
       <c r="M137" s="9" t="n"/>
       <c r="N137" s="9" t="n"/>
-      <c r="O137" s="22" t="n"/>
+      <c r="O137" s="9" t="n"/>
+      <c r="P137" s="22" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="12" t="n"/>
@@ -7515,7 +7689,8 @@
       <c r="L138" s="13" t="n"/>
       <c r="M138" s="13" t="n"/>
       <c r="N138" s="13" t="n"/>
-      <c r="O138" s="24" t="n"/>
+      <c r="O138" s="13" t="n"/>
+      <c r="P138" s="24" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="8" t="n"/>
@@ -7532,7 +7707,8 @@
       <c r="L139" s="9" t="n"/>
       <c r="M139" s="9" t="n"/>
       <c r="N139" s="9" t="n"/>
-      <c r="O139" s="22" t="n"/>
+      <c r="O139" s="9" t="n"/>
+      <c r="P139" s="22" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="12" t="n"/>
@@ -7549,14 +7725,15 @@
       <c r="L140" s="13" t="n"/>
       <c r="M140" s="13" t="n"/>
       <c r="N140" s="13" t="n"/>
-      <c r="O140" s="24" t="n"/>
+      <c r="O140" s="13" t="n"/>
+      <c r="P140" s="24" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1268,7 +1277,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="102" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 구매팀 │ 2026</t>
         </is>
@@ -1290,7 +1299,7 @@
       <c r="P1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="103" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 구매팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1307,11 +1316,13 @@
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="17" t="n"/>
-      <c r="N2" s="104" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
-        </is>
-      </c>
+      <c r="N2" s="107" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:58</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="n"/>
+      <c r="P2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -7731,9 +7742,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="3">
-    <mergeCell ref="N2:P2"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:P2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="P5:P109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_구매팀_입력_2026.xlsx
@@ -648,30 +648,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -685,86 +670,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -775,19 +720,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -802,55 +739,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -859,19 +772,11 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 외주 발주일 (양산 외주발주)
+        <t>▣ 외주 발주일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-15
 • 외부업체에 양산 가공품을 ★실제 발주한 날짜★ 기입
@@ -879,19 +784,11 @@
 • 외주입고일과 짝 — 발주 후 입고까지 추적
 • 비워두면: 외주 미발주 상태
 • 구매팀 전용 컬럼 (양산 외주 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 외주 입고예정일 (외주 발주 후 예정)
+        <t>▣ 외주 입고예정일 (외주 발주 후 예정)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-07-15
 • 외주(자재·양산 가공품) 발주 시
@@ -900,63 +797,38 @@
   ▸ 발주 시 예정일 입력
   ▸ 실제 입고일과 비교 → 지연 여부 추적
   ▸ 비워두면: 미발주 또는 일정 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 외주 입고일 (양산 외주발주)
+        <t>▣ 외주 입고일 (양산 외주발주)
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD
 • 외부업체에서 양산 가공품이 실제 입고된 날짜
 • 비워두면: 대시보드 외주현황에 '진행중'
 • 입고일 입력 시: '입고완료' 자동 분류</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1502,7 +1374,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1610,7 +1482,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1718,7 +1590,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1772,7 +1644,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1826,7 +1698,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1880,7 +1752,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1934,7 +1806,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1988,7 +1860,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -2042,7 +1914,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -2096,7 +1968,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -2150,7 +2022,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2204,7 +2076,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -2258,7 +2130,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2312,7 +2184,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2366,7 +2238,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2420,7 +2292,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2474,7 +2346,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2528,7 +2400,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2582,7 +2454,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2636,7 +2508,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2690,7 +2562,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2852,7 +2724,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2906,7 +2778,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2960,7 +2832,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -3014,7 +2886,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -3068,7 +2940,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -3122,7 +2994,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -3230,7 +3102,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -3284,7 +3156,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -3338,7 +3210,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -3500,7 +3372,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3554,7 +3426,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -3608,7 +3480,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3662,7 +3534,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3716,7 +3588,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3770,7 +3642,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3878,7 +3750,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3932,7 +3804,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3986,7 +3858,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -4040,7 +3912,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -4094,7 +3966,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -4148,7 +4020,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -4202,7 +4074,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -4256,7 +4128,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -4310,7 +4182,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -4364,7 +4236,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -4418,7 +4290,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -4526,7 +4398,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4580,7 +4452,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -4634,7 +4506,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -4688,7 +4560,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4796,7 +4668,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4850,7 +4722,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -4904,7 +4776,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4958,7 +4830,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -5012,7 +4884,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -5066,7 +4938,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -5120,7 +4992,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -5174,7 +5046,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -5228,7 +5100,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -5336,7 +5208,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -5390,7 +5262,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -5444,7 +5316,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -5498,7 +5370,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5552,7 +5424,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -5606,7 +5478,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5660,7 +5532,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -5714,7 +5586,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5876,7 +5748,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5930,7 +5802,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5984,7 +5856,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -6038,7 +5910,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -6092,7 +5964,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -6200,7 +6072,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -6254,7 +6126,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -6308,7 +6180,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -6362,7 +6234,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -6416,7 +6288,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -6470,7 +6342,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6524,7 +6396,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -6578,7 +6450,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6686,7 +6558,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6740,7 +6612,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -6794,7 +6666,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6848,7 +6720,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -6902,7 +6774,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -6956,7 +6828,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -7064,7 +6936,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -7168,7 +7040,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
